--- a/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.3-rescored.xlsx
+++ b/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.3-rescored.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="R4a73b04dfda14b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="Rd48c9dc2bdb34523"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -291,7 +291,7 @@
       <x:alignment vertical="bottom"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="95">
     <x:xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="bottom"/>
     </x:xf>
@@ -576,9 +576,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="59" fontId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <x:alignment vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -894,10 +891,6 @@
       <x:c r="N1"/>
       <x:c r="O1"/>
       <x:c r="P1"/>
-      <x:c r="Q1"/>
-      <x:c r="R1"/>
-      <x:c r="S1"/>
-      <x:c r="T1"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -932,18 +925,6 @@
       </x:c>
       <x:c r="O2" s="80"/>
       <x:c r="P2" s="80"/>
-      <x:c r="Q2" t="str">
-        <x:v>gpt-5-6-sol</x:v>
-      </x:c>
-      <x:c r="R2" t="str">
-        <x:v>gpt-5-6-sol</x:v>
-      </x:c>
-      <x:c r="S2" t="str">
-        <x:v>qwen3-8-flash</x:v>
-      </x:c>
-      <x:c r="T2" t="str">
-        <x:v>qwen3-8-flash</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="6"/>
@@ -970,18 +951,6 @@
       </x:c>
       <x:c r="O3" s="81"/>
       <x:c r="P3" s="81"/>
-      <x:c r="Q3" t="str">
-        <x:v>skill-on</x:v>
-      </x:c>
-      <x:c r="R3" t="str">
-        <x:v>skill-off</x:v>
-      </x:c>
-      <x:c r="S3" t="str">
-        <x:v>skill-on</x:v>
-      </x:c>
-      <x:c r="T3" t="str">
-        <x:v>skill-off</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="6"/>
@@ -992,48 +961,36 @@
         <x:v>作答结果</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>v0.9.1 得分</x:v>
+        <x:v>v0.9.2 得分</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>v0.9.2 得分</x:v>
+        <x:v>v0.9.3 得分</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
         <x:v>作答结果</x:v>
       </x:c>
       <x:c r="I4" s="9" t="str">
-        <x:v>v0.9.1 得分</x:v>
+        <x:v>v0.9.2 得分</x:v>
       </x:c>
       <x:c r="J4" s="9" t="str">
-        <x:v>v0.9.2 得分</x:v>
+        <x:v>v0.9.3 得分</x:v>
       </x:c>
       <x:c r="K4" s="9" t="str">
         <x:v>作答结果</x:v>
       </x:c>
       <x:c r="L4" s="9" t="str">
-        <x:v>v0.9.1 得分</x:v>
+        <x:v>v0.9.2 得分</x:v>
       </x:c>
       <x:c r="M4" s="82" t="str">
-        <x:v>v0.9.2 得分</x:v>
+        <x:v>v0.9.3 得分</x:v>
       </x:c>
       <x:c r="N4" s="82" t="str">
         <x:v>作答结果</x:v>
       </x:c>
       <x:c r="O4" s="82" t="str">
-        <x:v>v0.9.1 得分</x:v>
+        <x:v>v0.9.2 得分</x:v>
       </x:c>
       <x:c r="P4" s="82" t="str">
-        <x:v>v0.9.2 得分</x:v>
-      </x:c>
-      <x:c r="Q4" t="str">
-        <x:v>v0.9.3 得分</x:v>
-      </x:c>
-      <x:c r="R4" t="str">
-        <x:v>v0.9.3 得分</x:v>
-      </x:c>
-      <x:c r="S4" t="str">
-        <x:v>v0.9.3 得分</x:v>
-      </x:c>
-      <x:c r="T4" t="str">
         <x:v>v0.9.3 得分</x:v>
       </x:c>
     </x:row>
@@ -1066,7 +1023,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="J5" s="21" t="n">
-        <x:v>0.67</x:v>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="K5" s="11" t="str">
         <x:v>{"answer":-0.83,"unit":"kcal/mol"}</x:v>
@@ -1075,7 +1032,7 @@
         <x:v>0.996667</x:v>
       </x:c>
       <x:c r="M5" s="84" t="n">
-        <x:v>0.996667</x:v>
+        <x:v>0.9966666666666667</x:v>
       </x:c>
       <x:c r="N5" s="86" t="str">
         <x:v>{"answer":-0.68,"unit":"kcal/mol"}</x:v>
@@ -1084,18 +1041,6 @@
         <x:v>0.953333</x:v>
       </x:c>
       <x:c r="P5" s="84" t="n">
-        <x:v>0.953333</x:v>
-      </x:c>
-      <x:c r="Q5" s="95" t="n">
-        <x:v>0.996</x:v>
-      </x:c>
-      <x:c r="R5" s="95" t="n">
-        <x:v>0.6699999999999999</x:v>
-      </x:c>
-      <x:c r="S5" s="95" t="n">
-        <x:v>0.9966666666666667</x:v>
-      </x:c>
-      <x:c r="T5" s="95" t="n">
         <x:v>0.9533333333333334</x:v>
       </x:c>
     </x:row>
@@ -1119,7 +1064,7 @@
         <x:v>0.863333</x:v>
       </x:c>
       <x:c r="G6" s="24" t="n">
-        <x:v>0.863333</x:v>
+        <x:v>0.8633333333333333</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
         <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
@@ -1128,7 +1073,7 @@
         <x:v>0.863333</x:v>
       </x:c>
       <x:c r="J6" s="21" t="n">
-        <x:v>0.863333</x:v>
+        <x:v>0.8633333333333333</x:v>
       </x:c>
       <x:c r="K6" s="11" t="str">
         <x:v>{"answer":-5.87,"unit":"kcal/mol"}</x:v>
@@ -1146,18 +1091,6 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="P6" s="84" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="Q6" s="95" t="n">
-        <x:v>0.8633333333333333</x:v>
-      </x:c>
-      <x:c r="R6" s="95" t="n">
-        <x:v>0.8633333333333333</x:v>
-      </x:c>
-      <x:c r="S6" s="95" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="T6" s="95" t="n">
         <x:v>0.85</x:v>
       </x:c>
     </x:row>
@@ -1181,7 +1114,7 @@
         <x:v>0.883333</x:v>
       </x:c>
       <x:c r="G7" s="24" t="n">
-        <x:v>0.883333</x:v>
+        <x:v>0.8833333333333334</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
         <x:v>{"answer":-3.37,"unit":"kcal/mol"}</x:v>
@@ -1190,7 +1123,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="J7" s="21" t="n">
-        <x:v>0.58</x:v>
+        <x:v>0.5799999999999998</x:v>
       </x:c>
       <x:c r="K7" s="11" t="str">
         <x:v>{"answer":-2.0,"unit":"kcal/mol"}</x:v>
@@ -1199,7 +1132,7 @@
         <x:v>0.963333</x:v>
       </x:c>
       <x:c r="M7" s="84" t="n">
-        <x:v>0.963333</x:v>
+        <x:v>0.9633333333333334</x:v>
       </x:c>
       <x:c r="N7" s="86" t="str">
         <x:v>{"answer":-4.3,"unit":"kcal/mol"}</x:v>
@@ -1208,18 +1141,6 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="P7" s="84" t="n">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="Q7" s="95" t="n">
-        <x:v>0.8833333333333334</x:v>
-      </x:c>
-      <x:c r="R7" s="95" t="n">
-        <x:v>0.5799999999999998</x:v>
-      </x:c>
-      <x:c r="S7" s="95" t="n">
-        <x:v>0.9633333333333334</x:v>
-      </x:c>
-      <x:c r="T7" s="95" t="n">
         <x:v>0.27</x:v>
       </x:c>
     </x:row>
@@ -1243,7 +1164,7 @@
         <x:v>0.994496</x:v>
       </x:c>
       <x:c r="G8" s="24" t="n">
-        <x:v>0.994496</x:v>
+        <x:v>0.9944959999999999</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
         <x:v>{"answer":-3.26,"unit":"kcal/mol"}</x:v>
@@ -1252,7 +1173,7 @@
         <x:v>0.573333</x:v>
       </x:c>
       <x:c r="J8" s="21" t="n">
-        <x:v>0.573333</x:v>
+        <x:v>0.5733333333333335</x:v>
       </x:c>
       <x:c r="K8" s="11" t="str">
         <x:v>{"answer":-1.98,"unit":"kcal/mol"}</x:v>
@@ -1270,18 +1191,6 @@
         <x:v>0.976667</x:v>
       </x:c>
       <x:c r="P8" s="84" t="n">
-        <x:v>0.976667</x:v>
-      </x:c>
-      <x:c r="Q8" s="95" t="n">
-        <x:v>0.9944959999999999</x:v>
-      </x:c>
-      <x:c r="R8" s="95" t="n">
-        <x:v>0.5733333333333335</x:v>
-      </x:c>
-      <x:c r="S8" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T8" s="95" t="n">
         <x:v>0.9766666666666667</x:v>
       </x:c>
     </x:row>
@@ -1305,7 +1214,7 @@
         <x:v>0.85</x:v>
       </x:c>
       <x:c r="G9" s="24" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.8199999999999998</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
         <x:v>{"answer":-1.16,"unit":"V"}</x:v>
@@ -1314,7 +1223,7 @@
         <x:v>0.866667</x:v>
       </x:c>
       <x:c r="J9" s="21" t="n">
-        <x:v>0.866667</x:v>
+        <x:v>0.8399999999999999</x:v>
       </x:c>
       <x:c r="K9" s="11" t="str">
         <x:v>{"answer":-1.38,"unit":"V"}</x:v>
@@ -1323,7 +1232,7 @@
         <x:v>0.766667</x:v>
       </x:c>
       <x:c r="M9" s="84" t="n">
-        <x:v>0.766667</x:v>
+        <x:v>0.7200000000000002</x:v>
       </x:c>
       <x:c r="N9" s="86" t="str">
         <x:v>{"answer":-1.14,"unit":"V"}</x:v>
@@ -1332,18 +1241,6 @@
         <x:v>0.833333</x:v>
       </x:c>
       <x:c r="P9" s="84" t="n">
-        <x:v>0.833333</x:v>
-      </x:c>
-      <x:c r="Q9" s="95" t="n">
-        <x:v>0.8199999999999998</x:v>
-      </x:c>
-      <x:c r="R9" s="95" t="n">
-        <x:v>0.8399999999999999</x:v>
-      </x:c>
-      <x:c r="S9" s="95" t="n">
-        <x:v>0.7200000000000002</x:v>
-      </x:c>
-      <x:c r="T9" s="95" t="n">
         <x:v>0.7999999999999998</x:v>
       </x:c>
     </x:row>
@@ -1367,7 +1264,7 @@
         <x:v>0.883333</x:v>
       </x:c>
       <x:c r="G10" s="24" t="n">
-        <x:v>0.883333</x:v>
+        <x:v>0.8600000000000001</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
         <x:v>{"answer":0.24,"unit":"V"}</x:v>
@@ -1376,7 +1273,7 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="J10" s="21" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="K10" s="11" t="str">
         <x:v>{"answer":-0.34,"unit":"V"}</x:v>
@@ -1385,7 +1282,7 @@
         <x:v>0.083333</x:v>
       </x:c>
       <x:c r="M10" s="84" t="n">
-        <x:v>0.083333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="86" t="str">
         <x:v>{"answer":0.14,"unit":"V"}</x:v>
@@ -1394,18 +1291,6 @@
         <x:v>0.883333</x:v>
       </x:c>
       <x:c r="P10" s="84" t="n">
-        <x:v>0.883333</x:v>
-      </x:c>
-      <x:c r="Q10" s="95" t="n">
-        <x:v>0.8600000000000001</x:v>
-      </x:c>
-      <x:c r="R10" s="95" t="n">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="S10" s="95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T10" s="95" t="n">
         <x:v>0.8600000000000001</x:v>
       </x:c>
     </x:row>
@@ -1429,7 +1314,7 @@
         <x:v>0.966667</x:v>
       </x:c>
       <x:c r="G11" s="24" t="n">
-        <x:v>0.966667</x:v>
+        <x:v>0.9600000000000002</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
         <x:v>{"answer":0.72,"unit":"V"}</x:v>
@@ -1438,7 +1323,7 @@
         <x:v>0.816667</x:v>
       </x:c>
       <x:c r="J11" s="21" t="n">
-        <x:v>0.816667</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="K11" s="11" t="str">
         <x:v>{"answer":0.99,"unit":"V"}</x:v>
@@ -1447,7 +1332,7 @@
         <x:v>0.733333</x:v>
       </x:c>
       <x:c r="M11" s="84" t="n">
-        <x:v>0.733333</x:v>
+        <x:v>0.6799999999999999</x:v>
       </x:c>
       <x:c r="N11" s="86" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
@@ -1456,18 +1341,6 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="P11" s="84" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="Q11" s="95" t="n">
-        <x:v>0.9600000000000002</x:v>
-      </x:c>
-      <x:c r="R11" s="95" t="n">
-        <x:v>0.78</x:v>
-      </x:c>
-      <x:c r="S11" s="95" t="n">
-        <x:v>0.6799999999999999</x:v>
-      </x:c>
-      <x:c r="T11" s="95" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
@@ -1491,7 +1364,7 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="G12" s="24" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
@@ -1500,7 +1373,7 @@
         <x:v>0.933333</x:v>
       </x:c>
       <x:c r="J12" s="21" t="n">
-        <x:v>0.933333</x:v>
+        <x:v>0.9199999999999999</x:v>
       </x:c>
       <x:c r="K12" s="11" t="str">
         <x:v>{"answer":0.88,"unit":"V"}</x:v>
@@ -1509,7 +1382,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="M12" s="84" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.8799999999999999</x:v>
       </x:c>
       <x:c r="N12" s="86" t="str">
         <x:v>{"answer":0.85,"unit":"V"}</x:v>
@@ -1518,18 +1391,6 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="P12" s="84" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="Q12" s="95" t="n">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="R12" s="95" t="n">
-        <x:v>0.9199999999999999</x:v>
-      </x:c>
-      <x:c r="S12" s="95" t="n">
-        <x:v>0.8799999999999999</x:v>
-      </x:c>
-      <x:c r="T12" s="95" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
@@ -1553,7 +1414,7 @@
         <x:v>0.583333</x:v>
       </x:c>
       <x:c r="G13" s="24" t="n">
-        <x:v>0.583333</x:v>
+        <x:v>0.4999999999999998</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
         <x:v>{"answer":0.93,"unit":"V"}</x:v>
@@ -1562,7 +1423,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="J13" s="21" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.6399999999999999</x:v>
       </x:c>
       <x:c r="K13" s="11" t="str">
         <x:v>{"answer":1.06,"unit":"V"}</x:v>
@@ -1571,7 +1432,7 @@
         <x:v>0.916667</x:v>
       </x:c>
       <x:c r="M13" s="84" t="n">
-        <x:v>0.916667</x:v>
+        <x:v>0.8999999999999999</x:v>
       </x:c>
       <x:c r="N13" s="86" t="str">
         <x:v>{"answer":0.93,"unit":"V"}</x:v>
@@ -1580,18 +1441,6 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="P13" s="84" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="Q13" s="95" t="n">
-        <x:v>0.4999999999999998</x:v>
-      </x:c>
-      <x:c r="R13" s="95" t="n">
-        <x:v>0.6399999999999999</x:v>
-      </x:c>
-      <x:c r="S13" s="95" t="n">
-        <x:v>0.8999999999999999</x:v>
-      </x:c>
-      <x:c r="T13" s="95" t="n">
         <x:v>0.6399999999999999</x:v>
       </x:c>
     </x:row>
@@ -1615,7 +1464,7 @@
         <x:v>0.983333</x:v>
       </x:c>
       <x:c r="G14" s="24" t="n">
-        <x:v>0.983333</x:v>
+        <x:v>0.9500000000000002</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str">
         <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
@@ -1624,7 +1473,7 @@
         <x:v>0.983333</x:v>
       </x:c>
       <x:c r="J14" s="21" t="n">
-        <x:v>0.983333</x:v>
+        <x:v>0.9500000000000002</x:v>
       </x:c>
       <x:c r="K14" s="11" t="str">
         <x:v>{"answer":-4.4,"unit":"kcal/mol"}</x:v>
@@ -1633,7 +1482,7 @@
         <x:v>0.81</x:v>
       </x:c>
       <x:c r="M14" s="84" t="n">
-        <x:v>0.81</x:v>
+        <x:v>0.4300000000000006</x:v>
       </x:c>
       <x:c r="N14" s="86" t="str">
         <x:v>{"answer":-5.0,"unit":"kcal/mol"}</x:v>
@@ -1642,18 +1491,6 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="P14" s="84" t="n">
-        <x:v>0.99</x:v>
-      </x:c>
-      <x:c r="Q14" s="95" t="n">
-        <x:v>0.9500000000000002</x:v>
-      </x:c>
-      <x:c r="R14" s="95" t="n">
-        <x:v>0.9500000000000002</x:v>
-      </x:c>
-      <x:c r="S14" s="95" t="n">
-        <x:v>0.4300000000000006</x:v>
-      </x:c>
-      <x:c r="T14" s="95" t="n">
         <x:v>0.9699999999999998</x:v>
       </x:c>
     </x:row>
@@ -1677,7 +1514,7 @@
         <x:v>0.637376</x:v>
       </x:c>
       <x:c r="G15" s="24" t="n">
-        <x:v>0.637376</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="12" t="str">
         <x:v>{"answer":-3.17,"unit":"kcal/mol"}</x:v>
@@ -1686,7 +1523,7 @@
         <x:v>0.893333</x:v>
       </x:c>
       <x:c r="J15" s="21" t="n">
-        <x:v>0.893333</x:v>
+        <x:v>0.6800000000000002</x:v>
       </x:c>
       <x:c r="K15" s="11" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
@@ -1704,18 +1541,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P15" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q15" s="95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R15" s="95" t="n">
-        <x:v>0.6800000000000002</x:v>
-      </x:c>
-      <x:c r="S15" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T15" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1739,7 +1564,7 @@
         <x:v>0.913333</x:v>
       </x:c>
       <x:c r="G16" s="24" t="n">
-        <x:v>0.913333</x:v>
+        <x:v>0.7399999999999998</x:v>
       </x:c>
       <x:c r="H16" s="12" t="str">
         <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
@@ -1748,7 +1573,7 @@
         <x:v>0.913333</x:v>
       </x:c>
       <x:c r="J16" s="21" t="n">
-        <x:v>0.913333</x:v>
+        <x:v>0.7399999999999998</x:v>
       </x:c>
       <x:c r="K16" s="11" t="str">
         <x:v>{"answer":-2.25,"unit":"kcal/mol"}</x:v>
@@ -1757,7 +1582,7 @@
         <x:v>0.923333</x:v>
       </x:c>
       <x:c r="M16" s="84" t="n">
-        <x:v>0.923333</x:v>
+        <x:v>0.77</x:v>
       </x:c>
       <x:c r="N16" s="86" t="str">
         <x:v>{"answer":-2.4,"unit":"kcal/mol"}</x:v>
@@ -1766,18 +1591,6 @@
         <x:v>0.973333</x:v>
       </x:c>
       <x:c r="P16" s="84" t="n">
-        <x:v>0.973333</x:v>
-      </x:c>
-      <x:c r="Q16" s="95" t="n">
-        <x:v>0.7399999999999998</x:v>
-      </x:c>
-      <x:c r="R16" s="95" t="n">
-        <x:v>0.7399999999999998</x:v>
-      </x:c>
-      <x:c r="S16" s="95" t="n">
-        <x:v>0.77</x:v>
-      </x:c>
-      <x:c r="T16" s="95" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
     </x:row>
@@ -1801,7 +1614,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="G17" s="24" t="n">
-        <x:v>0.92</x:v>
+        <x:v>0.759999999999998</x:v>
       </x:c>
       <x:c r="H17" s="12" t="str">
         <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
@@ -1810,7 +1623,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="J17" s="21" t="n">
-        <x:v>0.92</x:v>
+        <x:v>0.759999999999998</x:v>
       </x:c>
       <x:c r="K17" s="11" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
@@ -1828,18 +1641,6 @@
         <x:v>0.886667</x:v>
       </x:c>
       <x:c r="P17" s="84" t="n">
-        <x:v>0.886667</x:v>
-      </x:c>
-      <x:c r="Q17" s="95" t="n">
-        <x:v>0.759999999999998</x:v>
-      </x:c>
-      <x:c r="R17" s="95" t="n">
-        <x:v>0.759999999999998</x:v>
-      </x:c>
-      <x:c r="S17" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T17" s="95" t="n">
         <x:v>0.6600000000000001</x:v>
       </x:c>
     </x:row>
@@ -1863,7 +1664,7 @@
         <x:v>0.926667</x:v>
       </x:c>
       <x:c r="G18" s="24" t="n">
-        <x:v>0.926667</x:v>
+        <x:v>0.7799999999999994</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str">
         <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
@@ -1872,7 +1673,7 @@
         <x:v>0.926667</x:v>
       </x:c>
       <x:c r="J18" s="21" t="n">
-        <x:v>0.926667</x:v>
+        <x:v>0.7799999999999994</x:v>
       </x:c>
       <x:c r="K18" s="11" t="str">
         <x:v>{"answer":-4.87,"unit":"kcal/mol"}</x:v>
@@ -1881,7 +1682,7 @@
         <x:v>0.993333</x:v>
       </x:c>
       <x:c r="M18" s="84" t="n">
-        <x:v>0.993333</x:v>
+        <x:v>0.9800000000000004</x:v>
       </x:c>
       <x:c r="N18" s="86" t="str">
         <x:v>{"answer":-4.96,"unit":"kcal/mol"}</x:v>
@@ -1890,18 +1691,6 @@
         <x:v>0.976667</x:v>
       </x:c>
       <x:c r="P18" s="84" t="n">
-        <x:v>0.976667</x:v>
-      </x:c>
-      <x:c r="Q18" s="95" t="n">
-        <x:v>0.7799999999999994</x:v>
-      </x:c>
-      <x:c r="R18" s="95" t="n">
-        <x:v>0.7799999999999994</x:v>
-      </x:c>
-      <x:c r="S18" s="95" t="n">
-        <x:v>0.9800000000000004</x:v>
-      </x:c>
-      <x:c r="T18" s="95" t="n">
         <x:v>0.9299999999999997</x:v>
       </x:c>
     </x:row>
@@ -1925,7 +1714,7 @@
         <x:v>0.295333</x:v>
       </x:c>
       <x:c r="G19" s="24" t="n">
-        <x:v>0.295333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str">
         <x:v>{"answer":-1.53,"unit":"kcal/mol"}</x:v>
@@ -1934,7 +1723,7 @@
         <x:v>0.933333</x:v>
       </x:c>
       <x:c r="J19" s="21" t="n">
-        <x:v>0.933333</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="K19" s="11" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
@@ -1952,18 +1741,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P19" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q19" s="95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R19" s="95" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="S19" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T19" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1987,7 +1764,7 @@
         <x:v>0.999728</x:v>
       </x:c>
       <x:c r="G20" s="24" t="n">
-        <x:v>0.999728</x:v>
+        <x:v>0.9996596677434243</x:v>
       </x:c>
       <x:c r="H20" s="12" t="str">
         <x:v>{"answer":65.014427,"unit":"a.u."}</x:v>
@@ -1996,7 +1773,7 @@
         <x:v>0.999728</x:v>
       </x:c>
       <x:c r="J20" s="21" t="n">
-        <x:v>0.999728</x:v>
+        <x:v>0.9996595139209358</x:v>
       </x:c>
       <x:c r="K20" s="11" t="str">
         <x:v>{"answer":65.0135,"unit":"a.u."}</x:v>
@@ -2005,7 +1782,7 @@
         <x:v>0.999785</x:v>
       </x:c>
       <x:c r="M20" s="84" t="n">
-        <x:v>0.999785</x:v>
+        <x:v>0.9997308106445171</x:v>
       </x:c>
       <x:c r="N20" s="86" t="str">
         <x:v>{"answer":65.014,"unit":"a.u."}</x:v>
@@ -2014,18 +1791,6 @@
         <x:v>0.999754</x:v>
       </x:c>
       <x:c r="P20" s="84" t="n">
-        <x:v>0.999754</x:v>
-      </x:c>
-      <x:c r="Q20" s="95" t="n">
-        <x:v>0.9996596677434243</x:v>
-      </x:c>
-      <x:c r="R20" s="95" t="n">
-        <x:v>0.9996595139209358</x:v>
-      </x:c>
-      <x:c r="S20" s="95" t="n">
-        <x:v>0.9997308106445171</x:v>
-      </x:c>
-      <x:c r="T20" s="95" t="n">
         <x:v>0.999692355022305</x:v>
       </x:c>
     </x:row>
@@ -2049,7 +1814,7 @@
         <x:v>0.471773</x:v>
       </x:c>
       <x:c r="G21" s="24" t="n">
-        <x:v>0.471773</x:v>
+        <x:v>0.33971563282746386</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str">
         <x:v>{"answer":67.869889,"unit":"a.u."}</x:v>
@@ -2058,7 +1823,7 @@
         <x:v>0.999993</x:v>
       </x:c>
       <x:c r="J21" s="21" t="n">
-        <x:v>0.999993</x:v>
+        <x:v>0.999991822602033</x:v>
       </x:c>
       <x:c r="K21" s="11" t="str">
         <x:v>{"answer":67.8696,"unit":"a.u."}</x:v>
@@ -2067,7 +1832,7 @@
         <x:v>0.999976</x:v>
       </x:c>
       <x:c r="M21" s="84" t="n">
-        <x:v>0.999976</x:v>
+        <x:v>0.9999705318992191</x:v>
       </x:c>
       <x:c r="N21" s="86" t="str">
         <x:v>{"answer":67.87,"unit":"a.u."}</x:v>
@@ -2076,18 +1841,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P21" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q21" s="95" t="n">
-        <x:v>0.33971563282746386</x:v>
-      </x:c>
-      <x:c r="R21" s="95" t="n">
-        <x:v>0.999991822602033</x:v>
-      </x:c>
-      <x:c r="S21" s="95" t="n">
-        <x:v>0.9999705318992191</x:v>
-      </x:c>
-      <x:c r="T21" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2111,7 +1864,7 @@
         <x:v>0.999937</x:v>
       </x:c>
       <x:c r="G22" s="24" t="n">
-        <x:v>0.999937</x:v>
+        <x:v>0.9999210553868704</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str">
         <x:v>{"answer":95.531814,"unit":"a.u."}</x:v>
@@ -2120,7 +1873,7 @@
         <x:v>0.999086</x:v>
       </x:c>
       <x:c r="J22" s="21" t="n">
-        <x:v>0.999086</x:v>
+        <x:v>0.9988580253376614</x:v>
       </x:c>
       <x:c r="K22" s="11" t="str">
         <x:v>{"answer":101.7,"unit":"a.u."}</x:v>
@@ -2129,7 +1882,7 @@
         <x:v>0.74076</x:v>
       </x:c>
       <x:c r="M22" s="84" t="n">
-        <x:v>0.74076</x:v>
+        <x:v>0.6759501622866717</x:v>
       </x:c>
       <x:c r="N22" s="86" t="str">
         <x:v>{"answer":95.51,"unit":"a.u."}</x:v>
@@ -2138,18 +1891,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P22" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q22" s="95" t="n">
-        <x:v>0.9999210553868704</x:v>
-      </x:c>
-      <x:c r="R22" s="95" t="n">
-        <x:v>0.9988580253376614</x:v>
-      </x:c>
-      <x:c r="S22" s="95" t="n">
-        <x:v>0.6759501622866717</x:v>
-      </x:c>
-      <x:c r="T22" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2182,7 +1923,7 @@
         <x:v>0.999474</x:v>
       </x:c>
       <x:c r="J23" s="21" t="n">
-        <x:v>0.999474</x:v>
+        <x:v>0.9990791896869242</x:v>
       </x:c>
       <x:c r="K23" s="11" t="str">
         <x:v>{"answer":5.433,"unit":"Debye"}</x:v>
@@ -2191,7 +1932,7 @@
         <x:v>0.998421</x:v>
       </x:c>
       <x:c r="M23" s="84" t="n">
-        <x:v>0.998421</x:v>
+        <x:v>0.9972375690607733</x:v>
       </x:c>
       <x:c r="N23" s="86" t="str">
         <x:v>{"answer":5.434,"unit":"Debye"}</x:v>
@@ -2200,18 +1941,6 @@
         <x:v>0.997895</x:v>
       </x:c>
       <x:c r="P23" s="84" t="n">
-        <x:v>0.997895</x:v>
-      </x:c>
-      <x:c r="Q23" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R23" s="95" t="n">
-        <x:v>0.9990791896869242</x:v>
-      </x:c>
-      <x:c r="S23" s="95" t="n">
-        <x:v>0.9972375690607733</x:v>
-      </x:c>
-      <x:c r="T23" s="95" t="n">
         <x:v>0.9963167587476975</x:v>
       </x:c>
     </x:row>
@@ -2235,7 +1964,7 @@
         <x:v>0.99696</x:v>
       </x:c>
       <x:c r="G24" s="24" t="n">
-        <x:v>0.99696</x:v>
+        <x:v>0.9946808510638298</x:v>
       </x:c>
       <x:c r="H24" s="12" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
@@ -2244,7 +1973,7 @@
         <x:v>0.99696</x:v>
       </x:c>
       <x:c r="J24" s="21" t="n">
-        <x:v>0.99696</x:v>
+        <x:v>0.9946808510638298</x:v>
       </x:c>
       <x:c r="K24" s="11" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
@@ -2253,7 +1982,7 @@
         <x:v>0.99696</x:v>
       </x:c>
       <x:c r="M24" s="84" t="n">
-        <x:v>0.99696</x:v>
+        <x:v>0.9946808510638298</x:v>
       </x:c>
       <x:c r="N24" s="86" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
@@ -2262,18 +1991,6 @@
         <x:v>0.99696</x:v>
       </x:c>
       <x:c r="P24" s="84" t="n">
-        <x:v>0.99696</x:v>
-      </x:c>
-      <x:c r="Q24" s="95" t="n">
-        <x:v>0.9946808510638298</x:v>
-      </x:c>
-      <x:c r="R24" s="95" t="n">
-        <x:v>0.9946808510638298</x:v>
-      </x:c>
-      <x:c r="S24" s="95" t="n">
-        <x:v>0.9946808510638298</x:v>
-      </x:c>
-      <x:c r="T24" s="95" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
     </x:row>
@@ -2297,7 +2014,7 @@
         <x:v>0.998516</x:v>
       </x:c>
       <x:c r="G25" s="24" t="n">
-        <x:v>0.998516</x:v>
+        <x:v>0.9974025974025977</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str">
         <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
@@ -2306,7 +2023,7 @@
         <x:v>0.998516</x:v>
       </x:c>
       <x:c r="J25" s="21" t="n">
-        <x:v>0.998516</x:v>
+        <x:v>0.9974025974025977</x:v>
       </x:c>
       <x:c r="K25" s="11" t="str">
         <x:v>{"answer":3.851,"unit":"Debye"}</x:v>
@@ -2315,7 +2032,7 @@
         <x:v>0.999258</x:v>
       </x:c>
       <x:c r="M25" s="84" t="n">
-        <x:v>0.999258</x:v>
+        <x:v>0.9987012987012989</x:v>
       </x:c>
       <x:c r="N25" s="86" t="str">
         <x:v>{"answer":3.85,"unit":"Debye"}</x:v>
@@ -2324,18 +2041,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P25" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q25" s="95" t="n">
-        <x:v>0.9974025974025977</x:v>
-      </x:c>
-      <x:c r="R25" s="95" t="n">
-        <x:v>0.9974025974025977</x:v>
-      </x:c>
-      <x:c r="S25" s="95" t="n">
-        <x:v>0.9987012987012989</x:v>
-      </x:c>
-      <x:c r="T25" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2359,7 +2064,7 @@
         <x:v>0.999201</x:v>
       </x:c>
       <x:c r="G26" s="24" t="n">
-        <x:v>0.999201</x:v>
+        <x:v>0.9990000000000001</x:v>
       </x:c>
       <x:c r="H26" s="12" t="str">
         <x:v>{"answer":1.2522024,"unit":"dimensionless"}</x:v>
@@ -2368,7 +2073,7 @@
         <x:v>0.99999</x:v>
       </x:c>
       <x:c r="J26" s="21" t="n">
-        <x:v>0.99999</x:v>
+        <x:v>0.9999879999999997</x:v>
       </x:c>
       <x:c r="K26" s="11" t="str">
         <x:v>{"answer":1.2522,"unit":"dimensionless"}</x:v>
@@ -2386,18 +2091,6 @@
         <x:v>0.999601</x:v>
       </x:c>
       <x:c r="P26" s="84" t="n">
-        <x:v>0.999601</x:v>
-      </x:c>
-      <x:c r="Q26" s="95" t="n">
-        <x:v>0.9990000000000001</x:v>
-      </x:c>
-      <x:c r="R26" s="95" t="n">
-        <x:v>0.9999879999999997</x:v>
-      </x:c>
-      <x:c r="S26" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T26" s="95" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
@@ -2421,7 +2114,7 @@
         <x:v>0.93229</x:v>
       </x:c>
       <x:c r="G27" s="24" t="n">
-        <x:v>0.93229</x:v>
+        <x:v>0.8875000000000002</x:v>
       </x:c>
       <x:c r="H27" s="12" t="str">
         <x:v>{"answer":1.6615304058,"unit":"dimensionless"}</x:v>
@@ -2430,7 +2123,7 @@
         <x:v>0.999908</x:v>
       </x:c>
       <x:c r="J27" s="21" t="n">
-        <x:v>0.999908</x:v>
+        <x:v>0.9998479709999999</x:v>
       </x:c>
       <x:c r="K27" s="11" t="str">
         <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
@@ -2439,7 +2132,7 @@
         <x:v>0.999699</x:v>
       </x:c>
       <x:c r="M27" s="84" t="n">
-        <x:v>0.999699</x:v>
+        <x:v>0.9995</x:v>
       </x:c>
       <x:c r="N27" s="86" t="str">
         <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
@@ -2448,18 +2141,6 @@
         <x:v>0.999699</x:v>
       </x:c>
       <x:c r="P27" s="84" t="n">
-        <x:v>0.999699</x:v>
-      </x:c>
-      <x:c r="Q27" s="95" t="n">
-        <x:v>0.8875000000000002</x:v>
-      </x:c>
-      <x:c r="R27" s="95" t="n">
-        <x:v>0.9998479709999999</x:v>
-      </x:c>
-      <x:c r="S27" s="95" t="n">
-        <x:v>0.9995</x:v>
-      </x:c>
-      <x:c r="T27" s="95" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
@@ -2483,7 +2164,7 @@
         <x:v>0.995695</x:v>
       </x:c>
       <x:c r="G28" s="24" t="n">
-        <x:v>0.995695</x:v>
+        <x:v>0.9959999999999999</x:v>
       </x:c>
       <x:c r="H28" s="12" t="str">
         <x:v>{"answer":0.9661815181817287,"unit":"dimensionless"}</x:v>
@@ -2492,7 +2173,7 @@
         <x:v>0.801003</x:v>
       </x:c>
       <x:c r="J28" s="21" t="n">
-        <x:v>0.801003</x:v>
+        <x:v>0.8150924090913566</x:v>
       </x:c>
       <x:c r="K28" s="11" t="str">
         <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
@@ -2501,7 +2182,7 @@
         <x:v>0.995695</x:v>
       </x:c>
       <x:c r="M28" s="84" t="n">
-        <x:v>0.995695</x:v>
+        <x:v>0.9959999999999999</x:v>
       </x:c>
       <x:c r="N28" s="86" t="str">
         <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
@@ -2510,18 +2191,6 @@
         <x:v>0.995695</x:v>
       </x:c>
       <x:c r="P28" s="84" t="n">
-        <x:v>0.995695</x:v>
-      </x:c>
-      <x:c r="Q28" s="95" t="n">
-        <x:v>0.9959999999999999</x:v>
-      </x:c>
-      <x:c r="R28" s="95" t="n">
-        <x:v>0.8150924090913566</x:v>
-      </x:c>
-      <x:c r="S28" s="95" t="n">
-        <x:v>0.9959999999999999</x:v>
-      </x:c>
-      <x:c r="T28" s="95" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
     </x:row>
@@ -2545,7 +2214,7 @@
         <x:v>0.346869</x:v>
       </x:c>
       <x:c r="G29" s="24" t="n">
-        <x:v>0.346869</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="12" t="str">
         <x:v>{"answer":-26.0378553128,"unit":"kcal/mol"}</x:v>
@@ -2554,7 +2223,7 @@
         <x:v>0.991536</x:v>
       </x:c>
       <x:c r="J29" s="21" t="n">
-        <x:v>0.991536</x:v>
+        <x:v>0.9824289374399996</x:v>
       </x:c>
       <x:c r="K29" s="11" t="str">
         <x:v>{"answer":-26.0,"unit":"kcal/mol"}</x:v>
@@ -2563,7 +2232,7 @@
         <x:v>0.995183</x:v>
       </x:c>
       <x:c r="M29" s="84" t="n">
-        <x:v>0.995183</x:v>
+        <x:v>0.9899999999999999</x:v>
       </x:c>
       <x:c r="N29" s="86" t="str">
         <x:v>{"answer":-32.74,"unit":"kcal/mol"}</x:v>
@@ -2572,18 +2241,6 @@
         <x:v>0.345857</x:v>
       </x:c>
       <x:c r="P29" s="84" t="n">
-        <x:v>0.345857</x:v>
-      </x:c>
-      <x:c r="Q29" s="95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R29" s="95" t="n">
-        <x:v>0.9824289374399996</x:v>
-      </x:c>
-      <x:c r="S29" s="95" t="n">
-        <x:v>0.9899999999999999</x:v>
-      </x:c>
-      <x:c r="T29" s="95" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2607,7 +2264,7 @@
         <x:v>0.999335</x:v>
       </x:c>
       <x:c r="G30" s="24" t="n">
-        <x:v>0.999335</x:v>
+        <x:v>0.9986693280106466</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
         <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
@@ -2616,7 +2273,7 @@
         <x:v>0.999335</x:v>
       </x:c>
       <x:c r="J30" s="21" t="n">
-        <x:v>0.999335</x:v>
+        <x:v>0.9986693280106466</x:v>
       </x:c>
       <x:c r="K30" s="11" t="str">
         <x:v>{"answer":137.5,"unit":"angstrom^2"}</x:v>
@@ -2625,7 +2282,7 @@
         <x:v>0.574185</x:v>
       </x:c>
       <x:c r="M30" s="84" t="n">
-        <x:v>0.574185</x:v>
+        <x:v>0.14836992681303984</x:v>
       </x:c>
       <x:c r="N30" s="86" t="str">
         <x:v>{"answer":135.4,"unit":"angstrom^2"}</x:v>
@@ -2634,18 +2291,6 @@
         <x:v>0.504325</x:v>
       </x:c>
       <x:c r="P30" s="84" t="n">
-        <x:v>0.504325</x:v>
-      </x:c>
-      <x:c r="Q30" s="95" t="n">
-        <x:v>0.9986693280106466</x:v>
-      </x:c>
-      <x:c r="R30" s="95" t="n">
-        <x:v>0.9986693280106466</x:v>
-      </x:c>
-      <x:c r="S30" s="95" t="n">
-        <x:v>0.14836992681303984</x:v>
-      </x:c>
-      <x:c r="T30" s="95" t="n">
         <x:v>0.008649367930804619</x:v>
       </x:c>
     </x:row>
@@ -2669,7 +2314,7 @@
         <x:v>0.975957</x:v>
       </x:c>
       <x:c r="G31" s="24" t="n">
-        <x:v>0.975957</x:v>
+        <x:v>0.9719495091164095</x:v>
       </x:c>
       <x:c r="H31" s="12" t="str">
         <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
@@ -2678,7 +2323,7 @@
         <x:v>0.975957</x:v>
       </x:c>
       <x:c r="J31" s="21" t="n">
-        <x:v>0.975957</x:v>
+        <x:v>0.9719495091164095</x:v>
       </x:c>
       <x:c r="K31" s="11" t="str">
         <x:v>{"answer":231.4,"unit":"(kcal/mol)^2"}</x:v>
@@ -2687,7 +2332,7 @@
         <x:v>0.148067</x:v>
       </x:c>
       <x:c r="M31" s="84" t="n">
-        <x:v>0.148067</x:v>
+        <x:v>0.006077606358111165</x:v>
       </x:c>
       <x:c r="N31" s="86" t="str">
         <x:v>{"answer":323.6,"unit":"(kcal/mol)^2"}</x:v>
@@ -2696,18 +2341,6 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P31" s="84" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q31" s="95" t="n">
-        <x:v>0.9719495091164095</x:v>
-      </x:c>
-      <x:c r="R31" s="95" t="n">
-        <x:v>0.9719495091164095</x:v>
-      </x:c>
-      <x:c r="S31" s="95" t="n">
-        <x:v>0.006077606358111165</x:v>
-      </x:c>
-      <x:c r="T31" s="95" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2731,7 +2364,7 @@
         <x:v>0.939122</x:v>
       </x:c>
       <x:c r="G32" s="24" t="n">
-        <x:v>0.939122</x:v>
+        <x:v>0.8782445611402854</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str">
         <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
@@ -2740,7 +2373,7 @@
         <x:v>0.939985</x:v>
       </x:c>
       <x:c r="J32" s="21" t="n">
-        <x:v>0.939985</x:v>
+        <x:v>0.8799699924981245</x:v>
       </x:c>
       <x:c r="K32" s="11" t="str">
         <x:v>{"answer":1.353,"unit":"g/cm^3"}</x:v>
@@ -2749,7 +2382,7 @@
         <x:v>0.924981</x:v>
       </x:c>
       <x:c r="M32" s="84" t="n">
-        <x:v>0.924981</x:v>
+        <x:v>0.8499624906226555</x:v>
       </x:c>
       <x:c r="N32" s="86" t="str">
         <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
@@ -2758,18 +2391,6 @@
         <x:v>0.939985</x:v>
       </x:c>
       <x:c r="P32" s="84" t="n">
-        <x:v>0.939985</x:v>
-      </x:c>
-      <x:c r="Q32" s="95" t="n">
-        <x:v>0.8782445611402854</x:v>
-      </x:c>
-      <x:c r="R32" s="95" t="n">
-        <x:v>0.8799699924981245</x:v>
-      </x:c>
-      <x:c r="S32" s="95" t="n">
-        <x:v>0.8499624906226555</x:v>
-      </x:c>
-      <x:c r="T32" s="95" t="n">
         <x:v>0.8799699924981245</x:v>
       </x:c>
     </x:row>
@@ -2793,7 +2414,7 @@
         <x:v>0.94152</x:v>
       </x:c>
       <x:c r="G33" s="24" t="n">
-        <x:v>0.94152</x:v>
+        <x:v>0.8830409356725145</x:v>
       </x:c>
       <x:c r="H33" s="12" t="str">
         <x:v>{"answer":1.730,"unit":"g/cm^3"}</x:v>
@@ -2802,7 +2423,7 @@
         <x:v>0.94152</x:v>
       </x:c>
       <x:c r="J33" s="21" t="n">
-        <x:v>0.94152</x:v>
+        <x:v>0.8830409356725145</x:v>
       </x:c>
       <x:c r="K33" s="11" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
@@ -2811,7 +2432,7 @@
         <x:v>0.94152</x:v>
       </x:c>
       <x:c r="M33" s="84" t="n">
-        <x:v>0.94152</x:v>
+        <x:v>0.8830409356725145</x:v>
       </x:c>
       <x:c r="N33" s="86" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
@@ -2820,18 +2441,6 @@
         <x:v>0.94152</x:v>
       </x:c>
       <x:c r="P33" s="84" t="n">
-        <x:v>0.94152</x:v>
-      </x:c>
-      <x:c r="Q33" s="95" t="n">
-        <x:v>0.8830409356725145</x:v>
-      </x:c>
-      <x:c r="R33" s="95" t="n">
-        <x:v>0.8830409356725145</x:v>
-      </x:c>
-      <x:c r="S33" s="95" t="n">
-        <x:v>0.8830409356725145</x:v>
-      </x:c>
-      <x:c r="T33" s="95" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
     </x:row>
@@ -2855,7 +2464,7 @@
         <x:v>0.945931</x:v>
       </x:c>
       <x:c r="G34" s="24" t="n">
-        <x:v>0.945931</x:v>
+        <x:v>0.8918623702894591</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str">
         <x:v>{"answer":1.8527,"unit":"g/cm^3"}</x:v>
@@ -2864,7 +2473,7 @@
         <x:v>0.940743</x:v>
       </x:c>
       <x:c r="J34" s="21" t="n">
-        <x:v>0.940743</x:v>
+        <x:v>0.8814855270344072</x:v>
       </x:c>
       <x:c r="K34" s="11" t="str">
         <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
@@ -2873,7 +2482,7 @@
         <x:v>0.939924</x:v>
       </x:c>
       <x:c r="M34" s="84" t="n">
-        <x:v>0.939924</x:v>
+        <x:v>0.8798470780993991</x:v>
       </x:c>
       <x:c r="N34" s="86" t="str">
         <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
@@ -2882,18 +2491,6 @@
         <x:v>0.939924</x:v>
       </x:c>
       <x:c r="P34" s="84" t="n">
-        <x:v>0.939924</x:v>
-      </x:c>
-      <x:c r="Q34" s="95" t="n">
-        <x:v>0.8918623702894591</x:v>
-      </x:c>
-      <x:c r="R34" s="95" t="n">
-        <x:v>0.8814855270344072</x:v>
-      </x:c>
-      <x:c r="S34" s="95" t="n">
-        <x:v>0.8798470780993991</x:v>
-      </x:c>
-      <x:c r="T34" s="95" t="n">
         <x:v>0.8798470780993991</x:v>
       </x:c>
     </x:row>
@@ -2917,7 +2514,7 @@
         <x:v>0.958365</x:v>
       </x:c>
       <x:c r="G35" s="24" t="n">
-        <x:v>0.958365</x:v>
+        <x:v>0.9557000000000001</x:v>
       </x:c>
       <x:c r="H35" s="12" t="str">
         <x:v>{"answer":-0.274885,"unit":"dimensionless"}</x:v>
@@ -2926,7 +2523,7 @@
         <x:v>0.958247</x:v>
       </x:c>
       <x:c r="J35" s="21" t="n">
-        <x:v>0.958247</x:v>
+        <x:v>0.9555750000000001</x:v>
       </x:c>
       <x:c r="K35" s="11" t="str">
         <x:v>{"answer":-0.2748,"unit":"dimensionless"}</x:v>
@@ -2935,7 +2532,7 @@
         <x:v>0.958647</x:v>
       </x:c>
       <x:c r="M35" s="84" t="n">
-        <x:v>0.958647</x:v>
+        <x:v>0.9560000000000002</x:v>
       </x:c>
       <x:c r="N35" s="86" t="str">
         <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
@@ -2944,18 +2541,6 @@
         <x:v>0.958365</x:v>
       </x:c>
       <x:c r="P35" s="84" t="n">
-        <x:v>0.958365</x:v>
-      </x:c>
-      <x:c r="Q35" s="95" t="n">
-        <x:v>0.9557000000000001</x:v>
-      </x:c>
-      <x:c r="R35" s="95" t="n">
-        <x:v>0.9555750000000001</x:v>
-      </x:c>
-      <x:c r="S35" s="95" t="n">
-        <x:v>0.9560000000000002</x:v>
-      </x:c>
-      <x:c r="T35" s="95" t="n">
         <x:v>0.9557000000000001</x:v>
       </x:c>
     </x:row>
@@ -2979,7 +2564,7 @@
         <x:v>0.93049</x:v>
       </x:c>
       <x:c r="G36" s="24" t="n">
-        <x:v>0.93049</x:v>
+        <x:v>0.9163100000000002</x:v>
       </x:c>
       <x:c r="H36" s="12" t="str">
         <x:v>{"answer":0.284321053217,"unit":"dimensionless"}</x:v>
@@ -2988,7 +2573,7 @@
         <x:v>0.930735</x:v>
       </x:c>
       <x:c r="J36" s="21" t="n">
-        <x:v>0.930735</x:v>
+        <x:v>0.9166052660850001</x:v>
       </x:c>
       <x:c r="K36" s="11" t="str">
         <x:v>{"answer":0.2244,"unit":"dimensionless"}</x:v>
@@ -2997,7 +2582,7 @@
         <x:v>0.681894</x:v>
       </x:c>
       <x:c r="M36" s="84" t="n">
-        <x:v>0.681894</x:v>
+        <x:v>0.617</x:v>
       </x:c>
       <x:c r="N36" s="86" t="str">
         <x:v>{"answer":0.2842,"unit":"dimensionless"}</x:v>
@@ -3006,18 +2591,6 @@
         <x:v>0.930233</x:v>
       </x:c>
       <x:c r="P36" s="84" t="n">
-        <x:v>0.930233</x:v>
-      </x:c>
-      <x:c r="Q36" s="95" t="n">
-        <x:v>0.9163100000000002</x:v>
-      </x:c>
-      <x:c r="R36" s="95" t="n">
-        <x:v>0.9166052660850001</x:v>
-      </x:c>
-      <x:c r="S36" s="95" t="n">
-        <x:v>0.617</x:v>
-      </x:c>
-      <x:c r="T36" s="95" t="n">
         <x:v>0.9160000000000001</x:v>
       </x:c>
     </x:row>
@@ -3041,7 +2614,7 @@
         <x:v>0.910102</x:v>
       </x:c>
       <x:c r="G37" s="24" t="n">
-        <x:v>0.910102</x:v>
+        <x:v>0.8507689047062565</x:v>
       </x:c>
       <x:c r="H37" s="12" t="str">
         <x:v>{"answer":0.6829546990237992,"unit":"dimensionless"}</x:v>
@@ -3050,7 +2623,7 @@
         <x:v>0.192908</x:v>
       </x:c>
       <x:c r="J37" s="21" t="n">
-        <x:v>0.192908</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="11" t="str">
         <x:v>{"answer":0.445,"unit":"dimensionless"}</x:v>
@@ -3059,7 +2632,7 @@
         <x:v>0.909639</x:v>
       </x:c>
       <x:c r="M37" s="84" t="n">
-        <x:v>0.909639</x:v>
+        <x:v>0.8499999999999999</x:v>
       </x:c>
       <x:c r="N37" s="86" t="str">
         <x:v>{"answer":0.4449,"unit":"dimensionless"}</x:v>
@@ -3068,18 +2641,6 @@
         <x:v>0.90994</x:v>
       </x:c>
       <x:c r="P37" s="84" t="n">
-        <x:v>0.90994</x:v>
-      </x:c>
-      <x:c r="Q37" s="95" t="n">
-        <x:v>0.8507689047062565</x:v>
-      </x:c>
-      <x:c r="R37" s="95" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S37" s="95" t="n">
-        <x:v>0.8499999999999999</x:v>
-      </x:c>
-      <x:c r="T37" s="95" t="n">
         <x:v>0.8504999999999998</x:v>
       </x:c>
     </x:row>
@@ -3130,18 +2691,6 @@
         <x:v>0.998684</x:v>
       </x:c>
       <x:c r="P38" s="84" t="n">
-        <x:v>0.998684</x:v>
-      </x:c>
-      <x:c r="Q38" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R38" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S38" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T38" s="95" t="n">
         <x:v>0.998</x:v>
       </x:c>
     </x:row>
@@ -3192,18 +2741,6 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="P39" s="84" t="n">
-        <x:v>0.98</x:v>
-      </x:c>
-      <x:c r="Q39" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R39" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S39" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T39" s="95" t="n">
         <x:v>0.9780000000000001</x:v>
       </x:c>
     </x:row>
@@ -3245,7 +2782,7 @@
         <x:v>0.985714</x:v>
       </x:c>
       <x:c r="M40" s="84" t="n">
-        <x:v>0.985714</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="N40" s="86" t="str">
         <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
@@ -3254,18 +2791,6 @@
         <x:v>0.985714</x:v>
       </x:c>
       <x:c r="P40" s="84" t="n">
-        <x:v>0.985714</x:v>
-      </x:c>
-      <x:c r="Q40" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R40" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S40" s="95" t="n">
-        <x:v>0.98</x:v>
-      </x:c>
-      <x:c r="T40" s="95" t="n">
         <x:v>0.98</x:v>
       </x:c>
     </x:row>
@@ -3289,7 +2814,7 @@
         <x:v>0.957476</x:v>
       </x:c>
       <x:c r="G41" s="24" t="n">
-        <x:v>0.957476</x:v>
+        <x:v>0.9489717024895626</x:v>
       </x:c>
       <x:c r="H41" s="12" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
@@ -3298,7 +2823,7 @@
         <x:v>0.957476</x:v>
       </x:c>
       <x:c r="J41" s="21" t="n">
-        <x:v>0.957476</x:v>
+        <x:v>0.9489717024895626</x:v>
       </x:c>
       <x:c r="K41" s="11" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
@@ -3307,7 +2832,7 @@
         <x:v>0.957476</x:v>
       </x:c>
       <x:c r="M41" s="84" t="n">
-        <x:v>0.957476</x:v>
+        <x:v>0.9489717024895626</x:v>
       </x:c>
       <x:c r="N41" s="86" t="str">
         <x:v>{"answer":64.37,"unit":"cal/(mol*K)"}</x:v>
@@ -3316,18 +2841,6 @@
         <x:v>0.961342</x:v>
       </x:c>
       <x:c r="P41" s="84" t="n">
-        <x:v>0.961342</x:v>
-      </x:c>
-      <x:c r="Q41" s="95" t="n">
-        <x:v>0.9489717024895626</x:v>
-      </x:c>
-      <x:c r="R41" s="95" t="n">
-        <x:v>0.9489717024895626</x:v>
-      </x:c>
-      <x:c r="S41" s="95" t="n">
-        <x:v>0.9489717024895626</x:v>
-      </x:c>
-      <x:c r="T41" s="95" t="n">
         <x:v>0.9536106386268753</x:v>
       </x:c>
     </x:row>
@@ -3351,7 +2864,7 @@
         <x:v>0.976964</x:v>
       </x:c>
       <x:c r="G42" s="24" t="n">
-        <x:v>0.976964</x:v>
+        <x:v>0.9723565998617836</x:v>
       </x:c>
       <x:c r="H42" s="12" t="str">
         <x:v>{"answer":58.01,"unit":"cal/(mol*K)"}</x:v>
@@ -3360,7 +2873,7 @@
         <x:v>0.981283</x:v>
       </x:c>
       <x:c r="J42" s="21" t="n">
-        <x:v>0.981283</x:v>
+        <x:v>0.9775397373876995</x:v>
       </x:c>
       <x:c r="K42" s="11" t="str">
         <x:v>{"answer":57.88,"unit":"cal/(mol*K)"}</x:v>
@@ -3378,18 +2891,6 @@
         <x:v>0.958247</x:v>
       </x:c>
       <x:c r="P42" s="84" t="n">
-        <x:v>0.958247</x:v>
-      </x:c>
-      <x:c r="Q42" s="95" t="n">
-        <x:v>0.9723565998617836</x:v>
-      </x:c>
-      <x:c r="R42" s="95" t="n">
-        <x:v>0.9775397373876995</x:v>
-      </x:c>
-      <x:c r="S42" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T42" s="95" t="n">
         <x:v>0.9498963372494819</x:v>
       </x:c>
     </x:row>
@@ -3413,7 +2914,7 @@
         <x:v>0.916531</x:v>
       </x:c>
       <x:c r="G43" s="24" t="n">
-        <x:v>0.916531</x:v>
+        <x:v>0.8998375744450468</x:v>
       </x:c>
       <x:c r="H43" s="12" t="str">
         <x:v>{"answer":75.22,"unit":"cal/(mol*K)"}</x:v>
@@ -3422,7 +2923,7 @@
         <x:v>0.848854</x:v>
       </x:c>
       <x:c r="J43" s="21" t="n">
-        <x:v>0.848854</x:v>
+        <x:v>0.8186247969680558</x:v>
       </x:c>
       <x:c r="K43" s="11" t="str">
         <x:v>{"answer":73.85,"unit":"cal/(mol*K)"}</x:v>
@@ -3431,7 +2932,7 @@
         <x:v>0.996616</x:v>
       </x:c>
       <x:c r="M43" s="84" t="n">
-        <x:v>0.996616</x:v>
+        <x:v>0.9959393611261503</x:v>
       </x:c>
       <x:c r="N43" s="86" t="str">
         <x:v>{"answer":73.5,"unit":"cal/(mol*K)"}</x:v>
@@ -3440,18 +2941,6 @@
         <x:v>0.957138</x:v>
       </x:c>
       <x:c r="P43" s="84" t="n">
-        <x:v>0.957138</x:v>
-      </x:c>
-      <x:c r="Q43" s="95" t="n">
-        <x:v>0.8998375744450468</x:v>
-      </x:c>
-      <x:c r="R43" s="95" t="n">
-        <x:v>0.8186247969680558</x:v>
-      </x:c>
-      <x:c r="S43" s="95" t="n">
-        <x:v>0.9959393611261503</x:v>
-      </x:c>
-      <x:c r="T43" s="95" t="n">
         <x:v>0.9485652409312405</x:v>
       </x:c>
     </x:row>
@@ -3475,7 +2964,7 @@
         <x:v>0.977477</x:v>
       </x:c>
       <x:c r="G44" s="24" t="n">
-        <x:v>0.977477</x:v>
+        <x:v>0.9729729729729719</x:v>
       </x:c>
       <x:c r="H44" s="12" t="str">
         <x:v>{"answer":44.516,"unit":"cal/(mol*K)"}</x:v>
@@ -3484,7 +2973,7 @@
         <x:v>0.978228</x:v>
       </x:c>
       <x:c r="J44" s="21" t="n">
-        <x:v>0.978228</x:v>
+        <x:v>0.9738738738738739</x:v>
       </x:c>
       <x:c r="K44" s="11" t="str">
         <x:v>{"answer":44.5,"unit":"cal/(mol*K)"}</x:v>
@@ -3493,7 +2982,7 @@
         <x:v>0.981231</x:v>
       </x:c>
       <x:c r="M44" s="84" t="n">
-        <x:v>0.981231</x:v>
+        <x:v>0.9774774774774772</x:v>
       </x:c>
       <x:c r="N44" s="86" t="str">
         <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
@@ -3502,18 +2991,6 @@
         <x:v>0.977477</x:v>
       </x:c>
       <x:c r="P44" s="84" t="n">
-        <x:v>0.977477</x:v>
-      </x:c>
-      <x:c r="Q44" s="95" t="n">
-        <x:v>0.9729729729729719</x:v>
-      </x:c>
-      <x:c r="R44" s="95" t="n">
-        <x:v>0.9738738738738739</x:v>
-      </x:c>
-      <x:c r="S44" s="95" t="n">
-        <x:v>0.9774774774774772</x:v>
-      </x:c>
-      <x:c r="T44" s="95" t="n">
         <x:v>0.9729729729729719</x:v>
       </x:c>
     </x:row>
@@ -3537,7 +3014,7 @@
         <x:v>0.97221</x:v>
       </x:c>
       <x:c r="G45" s="24" t="n">
-        <x:v>0.97221</x:v>
+        <x:v>0.9666515679442517</x:v>
       </x:c>
       <x:c r="H45" s="12" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
@@ -3546,7 +3023,7 @@
         <x:v>0.972779</x:v>
       </x:c>
       <x:c r="J45" s="21" t="n">
-        <x:v>0.972779</x:v>
+        <x:v>0.9673344947735195</x:v>
       </x:c>
       <x:c r="K45" s="11" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
@@ -3555,7 +3032,7 @@
         <x:v>0.972779</x:v>
       </x:c>
       <x:c r="M45" s="84" t="n">
-        <x:v>0.972779</x:v>
+        <x:v>0.9673344947735195</x:v>
       </x:c>
       <x:c r="N45" s="86" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
@@ -3564,18 +3041,6 @@
         <x:v>0.972779</x:v>
       </x:c>
       <x:c r="P45" s="84" t="n">
-        <x:v>0.972779</x:v>
-      </x:c>
-      <x:c r="Q45" s="95" t="n">
-        <x:v>0.9666515679442517</x:v>
-      </x:c>
-      <x:c r="R45" s="95" t="n">
-        <x:v>0.9673344947735195</x:v>
-      </x:c>
-      <x:c r="S45" s="95" t="n">
-        <x:v>0.9673344947735195</x:v>
-      </x:c>
-      <x:c r="T45" s="95" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
     </x:row>
@@ -3599,7 +3064,7 @@
         <x:v>0.986297</x:v>
       </x:c>
       <x:c r="G46" s="24" t="n">
-        <x:v>0.986297</x:v>
+        <x:v>0.9835562719812427</x:v>
       </x:c>
       <x:c r="H46" s="12" t="str">
         <x:v>{"answer":51.10,"unit":"cal/(mol*K)"}</x:v>
@@ -3608,7 +3073,7 @@
         <x:v>0.986974</x:v>
       </x:c>
       <x:c r="J46" s="21" t="n">
-        <x:v>0.986974</x:v>
+        <x:v>0.9843688940992579</x:v>
       </x:c>
       <x:c r="K46" s="11" t="str">
         <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
@@ -3617,7 +3082,7 @@
         <x:v>0.986974</x:v>
       </x:c>
       <x:c r="M46" s="84" t="n">
-        <x:v>0.986974</x:v>
+        <x:v>0.9843688940992579</x:v>
       </x:c>
       <x:c r="N46" s="86" t="str">
         <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
@@ -3626,18 +3091,6 @@
         <x:v>0.986974</x:v>
       </x:c>
       <x:c r="P46" s="84" t="n">
-        <x:v>0.986974</x:v>
-      </x:c>
-      <x:c r="Q46" s="95" t="n">
-        <x:v>0.9835562719812427</x:v>
-      </x:c>
-      <x:c r="R46" s="95" t="n">
-        <x:v>0.9843688940992579</x:v>
-      </x:c>
-      <x:c r="S46" s="95" t="n">
-        <x:v>0.9843688940992579</x:v>
-      </x:c>
-      <x:c r="T46" s="95" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
     </x:row>
@@ -3661,7 +3114,7 @@
         <x:v>0.999133</x:v>
       </x:c>
       <x:c r="G47" s="24" t="n">
-        <x:v>0.999133</x:v>
+        <x:v>0.999133333333333</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
         <x:v>{"answer":-16.04,"unit":"kcal/mol"}</x:v>
@@ -3679,7 +3132,7 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="M47" s="84" t="n">
-        <x:v>0.97</x:v>
+        <x:v>0.9700000000000001</x:v>
       </x:c>
       <x:c r="N47" s="86" t="str">
         <x:v>{"answer":-17.2,"unit":"kcal/mol"}</x:v>
@@ -3688,18 +3141,6 @@
         <x:v>0.613333</x:v>
       </x:c>
       <x:c r="P47" s="84" t="n">
-        <x:v>0.613333</x:v>
-      </x:c>
-      <x:c r="Q47" s="95" t="n">
-        <x:v>0.999133333333333</x:v>
-      </x:c>
-      <x:c r="R47" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S47" s="95" t="n">
-        <x:v>0.9700000000000001</x:v>
-      </x:c>
-      <x:c r="T47" s="95" t="n">
         <x:v>0.6133333333333333</x:v>
       </x:c>
     </x:row>
@@ -3752,18 +3193,6 @@
       <x:c r="P48" s="84" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q48" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R48" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S48" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T48" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="49" ht="76" customHeight="1">
       <x:c r="A49" s="10" t="str">
@@ -3785,7 +3214,7 @@
         <x:v>0.998657</x:v>
       </x:c>
       <x:c r="G49" s="24" t="n">
-        <x:v>0.998657</x:v>
+        <x:v>0.9975548666666666</x:v>
       </x:c>
       <x:c r="H49" s="12" t="str">
         <x:v>{"answer":0.3636,"unit":"e"}</x:v>
@@ -3794,7 +3223,7 @@
         <x:v>0.998535</x:v>
       </x:c>
       <x:c r="J49" s="21" t="n">
-        <x:v>0.998535</x:v>
+        <x:v>0.9973333333333333</x:v>
       </x:c>
       <x:c r="K49" s="11" t="str">
         <x:v>{"answer":0.3637,"unit":"e"}</x:v>
@@ -3803,7 +3232,7 @@
         <x:v>0.998901</x:v>
       </x:c>
       <x:c r="M49" s="84" t="n">
-        <x:v>0.998901</x:v>
+        <x:v>0.9980000000000002</x:v>
       </x:c>
       <x:c r="N49" s="86" t="str">
         <x:v>{"answer":0.364,"unit":"e"}</x:v>
@@ -3812,18 +3241,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P49" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q49" s="95" t="n">
-        <x:v>0.9975548666666666</x:v>
-      </x:c>
-      <x:c r="R49" s="95" t="n">
-        <x:v>0.9973333333333333</x:v>
-      </x:c>
-      <x:c r="S49" s="95" t="n">
-        <x:v>0.9980000000000002</x:v>
-      </x:c>
-      <x:c r="T49" s="95" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3876,18 +3293,6 @@
       <x:c r="P50" s="84" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q50" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R50" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S50" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T50" s="95" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="51" ht="76" customHeight="1">
       <x:c r="A51" s="10" t="str">
@@ -3909,7 +3314,7 @@
         <x:v>0.958</x:v>
       </x:c>
       <x:c r="G51" s="24" t="n">
-        <x:v>0.958</x:v>
+        <x:v>0.9160000000000004</x:v>
       </x:c>
       <x:c r="H51" s="12" t="str">
         <x:v>{"answer":4.08,"unit":"eV"}</x:v>
@@ -3918,7 +3323,7 @@
         <x:v>0.96</x:v>
       </x:c>
       <x:c r="J51" s="21" t="n">
-        <x:v>0.96</x:v>
+        <x:v>0.9199999999999999</x:v>
       </x:c>
       <x:c r="K51" s="11" t="str">
         <x:v>{"answer":4.078,"unit":"eV"}</x:v>
@@ -3927,7 +3332,7 @@
         <x:v>0.958</x:v>
       </x:c>
       <x:c r="M51" s="84" t="n">
-        <x:v>0.958</x:v>
+        <x:v>0.9160000000000004</x:v>
       </x:c>
       <x:c r="N51" s="86" t="str">
         <x:v>{"answer":4.08,"unit":"eV"}</x:v>
@@ -3936,18 +3341,6 @@
         <x:v>0.96</x:v>
       </x:c>
       <x:c r="P51" s="84" t="n">
-        <x:v>0.96</x:v>
-      </x:c>
-      <x:c r="Q51" s="95" t="n">
-        <x:v>0.9160000000000004</x:v>
-      </x:c>
-      <x:c r="R51" s="95" t="n">
-        <x:v>0.9199999999999999</x:v>
-      </x:c>
-      <x:c r="S51" s="95" t="n">
-        <x:v>0.9160000000000004</x:v>
-      </x:c>
-      <x:c r="T51" s="95" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
     </x:row>
@@ -3971,7 +3364,7 @@
         <x:v>0.9456</x:v>
       </x:c>
       <x:c r="G52" s="24" t="n">
-        <x:v>0.9456</x:v>
+        <x:v>0.8911999999999995</x:v>
       </x:c>
       <x:c r="H52" s="12" t="str">
         <x:v>{"answer":4.3655,"unit":"eV"}</x:v>
@@ -3980,7 +3373,7 @@
         <x:v>0.9455</x:v>
       </x:c>
       <x:c r="J52" s="21" t="n">
-        <x:v>0.9455</x:v>
+        <x:v>0.891</x:v>
       </x:c>
       <x:c r="K52" s="11" t="str">
         <x:v>{"answer":4.37,"unit":"eV"}</x:v>
@@ -3989,7 +3382,7 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="M52" s="84" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.9000000000000004</x:v>
       </x:c>
       <x:c r="N52" s="86" t="str">
         <x:v>{"answer":4.3657,"unit":"eV"}</x:v>
@@ -3998,18 +3391,6 @@
         <x:v>0.9457</x:v>
       </x:c>
       <x:c r="P52" s="84" t="n">
-        <x:v>0.9457</x:v>
-      </x:c>
-      <x:c r="Q52" s="95" t="n">
-        <x:v>0.8911999999999995</x:v>
-      </x:c>
-      <x:c r="R52" s="95" t="n">
-        <x:v>0.891</x:v>
-      </x:c>
-      <x:c r="S52" s="95" t="n">
-        <x:v>0.9000000000000004</x:v>
-      </x:c>
-      <x:c r="T52" s="95" t="n">
         <x:v>0.8914000000000009</x:v>
       </x:c>
     </x:row>
@@ -4033,7 +3414,7 @@
         <x:v>0.9388</x:v>
       </x:c>
       <x:c r="G53" s="24" t="n">
-        <x:v>0.9388</x:v>
+        <x:v>0.877600000000001</x:v>
       </x:c>
       <x:c r="H53" s="12" t="str">
         <x:v>{"answer":4.44869,"unit":"eV"}</x:v>
@@ -4042,7 +3423,7 @@
         <x:v>0.93869</x:v>
       </x:c>
       <x:c r="J53" s="21" t="n">
-        <x:v>0.93869</x:v>
+        <x:v>0.8773800000000005</x:v>
       </x:c>
       <x:c r="K53" s="11" t="str">
         <x:v>{"answer":4.449,"unit":"eV"}</x:v>
@@ -4051,7 +3432,7 @@
         <x:v>0.939</x:v>
       </x:c>
       <x:c r="M53" s="84" t="n">
-        <x:v>0.939</x:v>
+        <x:v>0.8780000000000001</x:v>
       </x:c>
       <x:c r="N53" s="86" t="str">
         <x:v>{"answer":4.449,"unit":"eV"}</x:v>
@@ -4060,18 +3441,6 @@
         <x:v>0.939</x:v>
       </x:c>
       <x:c r="P53" s="84" t="n">
-        <x:v>0.939</x:v>
-      </x:c>
-      <x:c r="Q53" s="95" t="n">
-        <x:v>0.877600000000001</x:v>
-      </x:c>
-      <x:c r="R53" s="95" t="n">
-        <x:v>0.8773800000000005</x:v>
-      </x:c>
-      <x:c r="S53" s="95" t="n">
-        <x:v>0.8780000000000001</x:v>
-      </x:c>
-      <x:c r="T53" s="95" t="n">
         <x:v>0.8780000000000001</x:v>
       </x:c>
     </x:row>
@@ -4095,7 +3464,7 @@
         <x:v>0.961</x:v>
       </x:c>
       <x:c r="G54" s="24" t="n">
-        <x:v>0.961</x:v>
+        <x:v>0.9220000000000006</x:v>
       </x:c>
       <x:c r="H54" s="12" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
@@ -4104,7 +3473,7 @@
         <x:v>0.961</x:v>
       </x:c>
       <x:c r="J54" s="21" t="n">
-        <x:v>0.961</x:v>
+        <x:v>0.9220000000000006</x:v>
       </x:c>
       <x:c r="K54" s="11" t="str">
         <x:v>{"answer":3.86,"unit":"eV"}</x:v>
@@ -4113,7 +3482,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="M54" s="84" t="n">
-        <x:v>0.82</x:v>
+        <x:v>0.6399999999999997</x:v>
       </x:c>
       <x:c r="N54" s="86" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
@@ -4122,18 +3491,6 @@
         <x:v>0.961</x:v>
       </x:c>
       <x:c r="P54" s="84" t="n">
-        <x:v>0.961</x:v>
-      </x:c>
-      <x:c r="Q54" s="95" t="n">
-        <x:v>0.9220000000000006</x:v>
-      </x:c>
-      <x:c r="R54" s="95" t="n">
-        <x:v>0.9220000000000006</x:v>
-      </x:c>
-      <x:c r="S54" s="95" t="n">
-        <x:v>0.6399999999999997</x:v>
-      </x:c>
-      <x:c r="T54" s="95" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
     </x:row>
@@ -4157,7 +3514,7 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="G55" s="25" t="n">
-        <x:v>0.97</x:v>
+        <x:v>0.9399999999999995</x:v>
       </x:c>
       <x:c r="H55" s="16" t="str">
         <x:v>{"answer":3.36,"unit":"eV"}</x:v>
@@ -4166,7 +3523,7 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="J55" s="22" t="n">
-        <x:v>0.97</x:v>
+        <x:v>0.9399999999999995</x:v>
       </x:c>
       <x:c r="K55" s="15" t="str">
         <x:v>{"answer":3.358,"unit":"eV"}</x:v>
@@ -4175,7 +3532,7 @@
         <x:v>0.968</x:v>
       </x:c>
       <x:c r="M55" s="91" t="n">
-        <x:v>0.968</x:v>
+        <x:v>0.9359999999999999</x:v>
       </x:c>
       <x:c r="N55" s="92" t="str">
         <x:v>{"answer":3.357,"unit":"eV"}</x:v>
@@ -4184,18 +3541,6 @@
         <x:v>0.967</x:v>
       </x:c>
       <x:c r="P55" s="91" t="n">
-        <x:v>0.967</x:v>
-      </x:c>
-      <x:c r="Q55" s="95" t="n">
-        <x:v>0.9399999999999995</x:v>
-      </x:c>
-      <x:c r="R55" s="95" t="n">
-        <x:v>0.9399999999999995</x:v>
-      </x:c>
-      <x:c r="S55" s="95" t="n">
-        <x:v>0.9359999999999999</x:v>
-      </x:c>
-      <x:c r="T55" s="95" t="n">
         <x:v>0.9340000000000002</x:v>
       </x:c>
     </x:row>
@@ -4213,7 +3558,7 @@
         <x:v>0.912676</x:v>
       </x:c>
       <x:c r="G56" s="23" t="n">
-        <x:v>0.912676</x:v>
+        <x:v>0.8606945680337507</x:v>
       </x:c>
       <x:c r="H56" s="20" t="str">
         <x:v>平均分</x:v>
@@ -4222,7 +3567,7 @@
         <x:v>0.915456</x:v>
       </x:c>
       <x:c r="J56" s="23" t="n">
-        <x:v>0.915456</x:v>
+        <x:v>0.8825376152069491</x:v>
       </x:c>
       <x:c r="K56" s="19" t="str">
         <x:v>平均分</x:v>
@@ -4231,7 +3576,7 @@
         <x:v>0.906391</x:v>
       </x:c>
       <x:c r="M56" s="93" t="n">
-        <x:v>0.906391</x:v>
+        <x:v>0.8647874743370195</x:v>
       </x:c>
       <x:c r="N56" s="94" t="str">
         <x:v>平均分</x:v>
@@ -4240,23 +3585,11 @@
         <x:v>0.898382</x:v>
       </x:c>
       <x:c r="P56" s="93" t="n">
-        <x:v>0.898382</x:v>
-      </x:c>
-      <x:c r="Q56" s="95" t="n">
-        <x:v>0.8606945680337507</x:v>
-      </x:c>
-      <x:c r="R56" s="95" t="n">
-        <x:v>0.8825376152069491</x:v>
-      </x:c>
-      <x:c r="S56" s="95" t="n">
-        <x:v>0.8647874743370195</x:v>
-      </x:c>
-      <x:c r="T56" s="95" t="n">
         <x:v>0.8619780245298304</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7d7d4ec232424d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34855bb098d4671"/>
 </x:worksheet>
 </file>
--- a/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.3-rescored.xlsx
+++ b/outputs/01a0b000-cf04-7f00-a568-1f20935b5dd8/vgb-property-calculation-basic-v0.9.3-rescored.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="Rde09b8c8e91e453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="1" r:id="Re7bb34f3751e4d65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -939,18 +939,18 @@
   <x:cols>
     <x:col min="1" max="1" width="21.984399795532227" style="1" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.031200408935547" style="1" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="21.125" style="1" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.335899353027344" style="1" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21.406200408935547" style="1" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.468799591064453" style="1" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15.72659969329834" style="1" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.851600646972656" style="1" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.765600204467773" style="1" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.171899795532227" style="1" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.335899353027344" style="1" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.406200408935547" style="1" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.468799591064453" style="1" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.72659969329834" style="1" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.851600646972656" style="1" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.765600204467773" style="1" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.171899795532227" style="1" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.796899795532227" style="1" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="13.796899795532227" style="1" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13.796899795532227" style="1" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15.171899795532227" style="1" hidden="0" customWidth="1"/>
     <x:col min="13" max="16384" width="8.85155963897705" style="1" customWidth="1"/>
-    <x:col min="13" max="13" width="15.171899795532227" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.796899795532227" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="13.796899795532227" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="13.796899795532227" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.796899795532227" hidden="0" customWidth="1"/>
@@ -973,7 +973,6 @@
       <x:c r="L1" s="102"/>
       <x:c r="M1" s="117"/>
       <x:c r="N1" s="117"/>
-      <x:c r="O1" s="117"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="97" t="str">
@@ -983,92 +982,87 @@
         <x:v>本题的标准答案</x:v>
       </x:c>
       <x:c r="C2" s="97" t="str">
-        <x:v>评分备注</x:v>
-      </x:c>
-      <x:c r="D2" s="97" t="str">
         <x:v>gpt-5-6-sol</x:v>
       </x:c>
+      <x:c r="D2" s="97"/>
       <x:c r="E2" s="107"/>
-      <x:c r="F2" s="97"/>
-      <x:c r="G2" s="107" t="str">
+      <x:c r="F2" s="97" t="str">
         <x:v>gpt-5-6-sol</x:v>
       </x:c>
+      <x:c r="G2" s="107"/>
       <x:c r="H2" s="97"/>
-      <x:c r="I2" s="107"/>
-      <x:c r="J2" s="97" t="str">
+      <x:c r="I2" s="107" t="str">
         <x:v>qwen3-8-flash</x:v>
       </x:c>
+      <x:c r="J2" s="97"/>
       <x:c r="K2" s="107"/>
-      <x:c r="L2" s="107"/>
-      <x:c r="M2" s="31" t="str">
+      <x:c r="L2" s="107" t="str">
         <x:v>qwen3-8-flash</x:v>
       </x:c>
+      <x:c r="M2" s="31"/>
       <x:c r="N2" s="31"/>
-      <x:c r="O2" s="31"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="98"/>
       <x:c r="B3" s="98"/>
-      <x:c r="C3" s="98"/>
-      <x:c r="D3" s="105" t="str">
+      <x:c r="C3" s="98" t="str">
         <x:v>skill-on</x:v>
       </x:c>
+      <x:c r="D3" s="105"/>
       <x:c r="E3" s="108"/>
-      <x:c r="F3" s="110"/>
-      <x:c r="G3" s="108" t="str">
+      <x:c r="F3" s="110" t="str">
         <x:v>skill-off</x:v>
       </x:c>
+      <x:c r="G3" s="108"/>
       <x:c r="H3" s="110"/>
-      <x:c r="I3" s="108"/>
-      <x:c r="J3" s="110" t="str">
+      <x:c r="I3" s="108" t="str">
         <x:v>skill-on</x:v>
       </x:c>
+      <x:c r="J3" s="110"/>
       <x:c r="K3" s="108"/>
-      <x:c r="L3" s="108"/>
-      <x:c r="M3" s="36" t="str">
+      <x:c r="L3" s="108" t="str">
         <x:v>skill-off</x:v>
       </x:c>
+      <x:c r="M3" s="36"/>
       <x:c r="N3" s="36"/>
-      <x:c r="O3" s="36"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="98"/>
       <x:c r="B4" s="98"/>
-      <x:c r="C4" s="98"/>
+      <x:c r="C4" s="98" t="str">
+        <x:v>作答结果</x:v>
+      </x:c>
       <x:c r="D4" s="105" t="str">
+        <x:v>v0.9.2 得分</x:v>
+      </x:c>
+      <x:c r="E4" s="109" t="str">
+        <x:v>v0.9.3 得分</x:v>
+      </x:c>
+      <x:c r="F4" s="109" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="E4" s="109" t="str">
+      <x:c r="G4" s="109" t="str">
         <x:v>v0.9.2 得分</x:v>
       </x:c>
-      <x:c r="F4" s="109" t="str">
+      <x:c r="H4" s="109" t="str">
         <x:v>v0.9.3 得分</x:v>
       </x:c>
-      <x:c r="G4" s="109" t="str">
+      <x:c r="I4" s="109" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="H4" s="109" t="str">
+      <x:c r="J4" s="109" t="str">
         <x:v>v0.9.2 得分</x:v>
       </x:c>
-      <x:c r="I4" s="109" t="str">
+      <x:c r="K4" s="109" t="str">
         <x:v>v0.9.3 得分</x:v>
       </x:c>
-      <x:c r="J4" s="109" t="str">
+      <x:c r="L4" s="116" t="str">
         <x:v>作答结果</x:v>
       </x:c>
-      <x:c r="K4" s="109" t="str">
+      <x:c r="M4" s="41" t="str">
         <x:v>v0.9.2 得分</x:v>
       </x:c>
-      <x:c r="L4" s="116" t="str">
-        <x:v>v0.9.3 得分</x:v>
-      </x:c>
-      <x:c r="M4" s="41" t="str">
-        <x:v>作答结果</x:v>
-      </x:c>
       <x:c r="N4" s="41" t="str">
-        <x:v>v0.9.2 得分</x:v>
-      </x:c>
-      <x:c r="O4" s="41" t="str">
         <x:v>v0.9.3 得分</x:v>
       </x:c>
     </x:row>
@@ -1080,42 +1074,39 @@
         <x:v>{"answer":-0.82,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C5" s="99" t="str">
-        <x:v>aqueous_solvation_free_energy：标准答案 -0.82 kcal/mol；版本 linear_goal_v2。满分：x=-0.82 kcal/mol。部分分：-3.82 &lt; x &lt; -0.82 或 -0.82 &lt; x &lt; 2.18（按绝对误差线性递减）。0分：x &lt;= -3.82 或 x &gt;= 2.18；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D5" s="99" t="str">
         <x:v>{"answer":-0.832,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="n">
+        <x:v>0.996</x:v>
       </x:c>
       <x:c r="E5" s="24" t="n">
         <x:v>0.996</x:v>
       </x:c>
-      <x:c r="F5" s="21" t="n">
-        <x:v>0.996</x:v>
-      </x:c>
-      <x:c r="G5" s="111" t="str">
+      <x:c r="F5" s="21" t="str">
         <x:v>{"answer":0.17,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G5" s="111" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
       <x:c r="H5" s="21" t="n">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="I5" s="24" t="n">
         <x:v>0.6699999999999999</x:v>
       </x:c>
-      <x:c r="J5" s="114" t="str">
+      <x:c r="I5" s="24" t="str">
         <x:v>{"answer":-0.83,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J5" s="114" t="n">
+        <x:v>0.996667</x:v>
+      </x:c>
       <x:c r="K5" s="24" t="n">
-        <x:v>0.996667</x:v>
-      </x:c>
-      <x:c r="L5" s="21" t="n">
         <x:v>0.9966666666666667</x:v>
       </x:c>
-      <x:c r="M5" s="118" t="str">
+      <x:c r="L5" s="21" t="str">
         <x:v>{"answer":-0.68,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M5" s="118" t="n">
+        <x:v>0.953333</x:v>
+      </x:c>
       <x:c r="N5" s="120" t="n">
-        <x:v>0.953333</x:v>
-      </x:c>
-      <x:c r="O5" s="122" t="n">
         <x:v>0.9533333333333334</x:v>
       </x:c>
     </x:row>
@@ -1127,42 +1118,39 @@
         <x:v>{"answer":-5.42,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C6" s="99" t="str">
-        <x:v>aqueous_solvation_free_energy：标准答案 -5.42 kcal/mol；版本 linear_goal_v2。满分：x=-5.42 kcal/mol。部分分：-8.42 &lt; x &lt; -5.42 或 -5.42 &lt; x &lt; -2.42（按绝对误差线性递减）。0分：x &lt;= -8.42 或 x &gt;= -2.42；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D6" s="99" t="str">
         <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D6" s="99" t="n">
+        <x:v>0.863333</x:v>
+      </x:c>
       <x:c r="E6" s="24" t="n">
+        <x:v>0.8633333333333333</x:v>
+      </x:c>
+      <x:c r="F6" s="21" t="str">
+        <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="G6" s="111" t="n">
         <x:v>0.863333</x:v>
       </x:c>
-      <x:c r="F6" s="21" t="n">
+      <x:c r="H6" s="21" t="n">
         <x:v>0.8633333333333333</x:v>
       </x:c>
-      <x:c r="G6" s="111" t="str">
-        <x:v>{"answer":-5.01,"unit":"kcal/mol"}</x:v>
-      </x:c>
-      <x:c r="H6" s="21" t="n">
-        <x:v>0.863333</x:v>
-      </x:c>
-      <x:c r="I6" s="24" t="n">
-        <x:v>0.8633333333333333</x:v>
-      </x:c>
-      <x:c r="J6" s="114" t="str">
+      <x:c r="I6" s="24" t="str">
         <x:v>{"answer":-5.87,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="J6" s="114" t="n">
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="K6" s="24" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="L6" s="21" t="n">
+      <x:c r="L6" s="21" t="str">
+        <x:v>{"answer":-4.97,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="M6" s="118" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="M6" s="118" t="str">
-        <x:v>{"answer":-4.97,"unit":"kcal/mol"}</x:v>
-      </x:c>
       <x:c r="N6" s="120" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="O6" s="122" t="n">
         <x:v>0.85</x:v>
       </x:c>
     </x:row>
@@ -1174,42 +1162,39 @@
         <x:v>{"answer":-2.11,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C7" s="99" t="str">
-        <x:v>aqueous_solvation_free_energy：标准答案 -2.11 kcal/mol；版本 linear_goal_v2。满分：x=-2.11 kcal/mol。部分分：-5.11 &lt; x &lt; -2.11 或 -2.11 &lt; x &lt; 0.89（按绝对误差线性递减）。0分：x &lt;= -5.11 或 x &gt;= 0.89；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D7" s="99" t="str">
         <x:v>{"answer":-1.76,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D7" s="99" t="n">
+        <x:v>0.883333</x:v>
+      </x:c>
       <x:c r="E7" s="24" t="n">
-        <x:v>0.883333</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="n">
         <x:v>0.8833333333333334</x:v>
       </x:c>
-      <x:c r="G7" s="111" t="str">
+      <x:c r="F7" s="21" t="str">
         <x:v>{"answer":-3.37,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G7" s="111" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
       <x:c r="H7" s="21" t="n">
-        <x:v>0.58</x:v>
-      </x:c>
-      <x:c r="I7" s="24" t="n">
         <x:v>0.5799999999999998</x:v>
       </x:c>
-      <x:c r="J7" s="114" t="str">
+      <x:c r="I7" s="24" t="str">
         <x:v>{"answer":-2.0,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J7" s="114" t="n">
+        <x:v>0.963333</x:v>
+      </x:c>
       <x:c r="K7" s="24" t="n">
-        <x:v>0.963333</x:v>
-      </x:c>
-      <x:c r="L7" s="21" t="n">
         <x:v>0.9633333333333334</x:v>
       </x:c>
-      <x:c r="M7" s="118" t="str">
+      <x:c r="L7" s="21" t="str">
         <x:v>{"answer":-4.3,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M7" s="118" t="n">
+        <x:v>0.27</x:v>
+      </x:c>
       <x:c r="N7" s="120" t="n">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="O7" s="122" t="n">
         <x:v>0.27</x:v>
       </x:c>
     </x:row>
@@ -1221,42 +1206,39 @@
         <x:v>{"answer":-1.98,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
-        <x:v>aqueous_solvation_free_energy：标准答案 -1.98 kcal/mol；版本 linear_goal_v2。满分：x=-1.98 kcal/mol。部分分：-4.98 &lt; x &lt; -1.98 或 -1.98 &lt; x &lt; 1.02（按绝对误差线性递减）。0分：x &lt;= -4.98 或 x &gt;= 1.02；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D8" s="99" t="str">
         <x:v>{"answer":-1.963488,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D8" s="99" t="n">
+        <x:v>0.994496</x:v>
+      </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>0.994496</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="n">
         <x:v>0.9944959999999999</x:v>
       </x:c>
-      <x:c r="G8" s="111" t="str">
+      <x:c r="F8" s="21" t="str">
         <x:v>{"answer":-3.26,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G8" s="111" t="n">
+        <x:v>0.573333</x:v>
+      </x:c>
       <x:c r="H8" s="21" t="n">
-        <x:v>0.573333</x:v>
-      </x:c>
-      <x:c r="I8" s="24" t="n">
         <x:v>0.5733333333333335</x:v>
       </x:c>
-      <x:c r="J8" s="114" t="str">
+      <x:c r="I8" s="24" t="str">
         <x:v>{"answer":-1.98,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J8" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K8" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M8" s="118" t="str">
+      <x:c r="L8" s="21" t="str">
         <x:v>{"answer":-2.05,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M8" s="118" t="n">
+        <x:v>0.976667</x:v>
+      </x:c>
       <x:c r="N8" s="120" t="n">
-        <x:v>0.976667</x:v>
-      </x:c>
-      <x:c r="O8" s="122" t="n">
         <x:v>0.9766666666666667</x:v>
       </x:c>
     </x:row>
@@ -1268,42 +1250,39 @@
         <x:v>{"answer":-1.24,"unit":"V"}</x:v>
       </x:c>
       <x:c r="C9" s="99" t="str">
-        <x:v>first_reduction_potential_vs_sce：标准答案 -1.24 V；版本 linear_goal_v2。满分：x=-1.24 V。部分分：-1.84 &lt; x &lt; -1.24 或 -1.24 &lt; x &lt; -0.64（按绝对误差线性递减）。0分：x &lt;= -1.84 或 x &gt;= -0.64；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D9" s="99" t="str">
         <x:v>{"answer":-1.15,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="D9" s="99" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="n">
         <x:v>0.8199999999999998</x:v>
       </x:c>
-      <x:c r="G9" s="111" t="str">
+      <x:c r="F9" s="21" t="str">
         <x:v>{"answer":-1.16,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="G9" s="111" t="n">
+        <x:v>0.866667</x:v>
+      </x:c>
       <x:c r="H9" s="21" t="n">
-        <x:v>0.866667</x:v>
-      </x:c>
-      <x:c r="I9" s="24" t="n">
         <x:v>0.8399999999999999</x:v>
       </x:c>
-      <x:c r="J9" s="114" t="str">
+      <x:c r="I9" s="24" t="str">
         <x:v>{"answer":-1.38,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="J9" s="114" t="n">
+        <x:v>0.766667</x:v>
+      </x:c>
       <x:c r="K9" s="24" t="n">
-        <x:v>0.766667</x:v>
-      </x:c>
-      <x:c r="L9" s="21" t="n">
         <x:v>0.7200000000000002</x:v>
       </x:c>
-      <x:c r="M9" s="118" t="str">
+      <x:c r="L9" s="21" t="str">
         <x:v>{"answer":-1.14,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="M9" s="118" t="n">
+        <x:v>0.833333</x:v>
+      </x:c>
       <x:c r="N9" s="120" t="n">
-        <x:v>0.833333</x:v>
-      </x:c>
-      <x:c r="O9" s="122" t="n">
         <x:v>0.7999999999999998</x:v>
       </x:c>
     </x:row>
@@ -1315,42 +1294,39 @@
         <x:v>{"answer":0.21,"unit":"V"}</x:v>
       </x:c>
       <x:c r="C10" s="99" t="str">
-        <x:v>first_reduction_potential_vs_sce：标准答案 0.21 V；版本 linear_goal_v2。满分：x=0.21 V。部分分：-0.39 &lt; x &lt; 0.21 或 0.21 &lt; x &lt; 0.81（按绝对误差线性递减）。0分：x &lt;= -0.39 或 x &gt;= 0.81；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D10" s="99" t="str">
         <x:v>{"answer":0.14,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="D10" s="99" t="n">
+        <x:v>0.883333</x:v>
+      </x:c>
       <x:c r="E10" s="24" t="n">
+        <x:v>0.8600000000000001</x:v>
+      </x:c>
+      <x:c r="F10" s="21" t="str">
+        <x:v>{"answer":0.24,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="G10" s="111" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="I10" s="24" t="str">
+        <x:v>{"answer":-0.34,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="J10" s="114" t="n">
+        <x:v>0.083333</x:v>
+      </x:c>
+      <x:c r="K10" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="21" t="str">
+        <x:v>{"answer":0.14,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="M10" s="118" t="n">
         <x:v>0.883333</x:v>
       </x:c>
-      <x:c r="F10" s="21" t="n">
-        <x:v>0.8600000000000001</x:v>
-      </x:c>
-      <x:c r="G10" s="111" t="str">
-        <x:v>{"answer":0.24,"unit":"V"}</x:v>
-      </x:c>
-      <x:c r="H10" s="21" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="I10" s="24" t="n">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="J10" s="114" t="str">
-        <x:v>{"answer":-0.34,"unit":"V"}</x:v>
-      </x:c>
-      <x:c r="K10" s="24" t="n">
-        <x:v>0.083333</x:v>
-      </x:c>
-      <x:c r="L10" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="118" t="str">
-        <x:v>{"answer":0.14,"unit":"V"}</x:v>
-      </x:c>
       <x:c r="N10" s="120" t="n">
-        <x:v>0.883333</x:v>
-      </x:c>
-      <x:c r="O10" s="122" t="n">
         <x:v>0.8600000000000001</x:v>
       </x:c>
     </x:row>
@@ -1362,42 +1338,39 @@
         <x:v>{"answer":0.83,"unit":"V"}</x:v>
       </x:c>
       <x:c r="C11" s="99" t="str">
-        <x:v>first_oxidation_potential_vs_sce：标准答案 0.83 V；版本 linear_goal_v2。满分：x=0.83 V。部分分：0.23 &lt; x &lt; 0.83 或 0.83 &lt; x &lt; 1.43（按绝对误差线性递减）。0分：x &lt;= 0.23 或 x &gt;= 1.43；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D11" s="99" t="str">
         <x:v>{"answer":0.81,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="D11" s="99" t="n">
+        <x:v>0.966667</x:v>
+      </x:c>
       <x:c r="E11" s="24" t="n">
-        <x:v>0.966667</x:v>
-      </x:c>
-      <x:c r="F11" s="21" t="n">
         <x:v>0.9600000000000002</x:v>
       </x:c>
-      <x:c r="G11" s="111" t="str">
+      <x:c r="F11" s="21" t="str">
         <x:v>{"answer":0.72,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="G11" s="111" t="n">
+        <x:v>0.816667</x:v>
+      </x:c>
       <x:c r="H11" s="21" t="n">
-        <x:v>0.816667</x:v>
-      </x:c>
-      <x:c r="I11" s="24" t="n">
         <x:v>0.78</x:v>
       </x:c>
-      <x:c r="J11" s="114" t="str">
+      <x:c r="I11" s="24" t="str">
         <x:v>{"answer":0.99,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="J11" s="114" t="n">
+        <x:v>0.733333</x:v>
+      </x:c>
       <x:c r="K11" s="24" t="n">
-        <x:v>0.733333</x:v>
-      </x:c>
-      <x:c r="L11" s="21" t="n">
         <x:v>0.6799999999999999</x:v>
       </x:c>
-      <x:c r="M11" s="118" t="str">
+      <x:c r="L11" s="21" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="M11" s="118" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
       <x:c r="N11" s="120" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="O11" s="122" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
@@ -1409,42 +1382,39 @@
         <x:v>{"answer":0.82,"unit":"V"}</x:v>
       </x:c>
       <x:c r="C12" s="99" t="str">
-        <x:v>first_oxidation_potential_vs_sce：标准答案 0.82 V；版本 linear_goal_v2。满分：x=0.82 V。部分分：0.22 &lt; x &lt; 0.82 或 0.82 &lt; x &lt; 1.42（按绝对误差线性递减）。0分：x &lt;= 0.22 或 x &gt;= 1.42；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D12" s="99" t="str">
         <x:v>{"answer":0.85,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="D12" s="99" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
       <x:c r="E12" s="24" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="F12" s="21" t="str">
+        <x:v>{"answer":0.86,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="G12" s="111" t="n">
+        <x:v>0.933333</x:v>
+      </x:c>
+      <x:c r="H12" s="21" t="n">
+        <x:v>0.9199999999999999</x:v>
+      </x:c>
+      <x:c r="I12" s="24" t="str">
+        <x:v>{"answer":0.88,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="J12" s="114" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K12" s="24" t="n">
+        <x:v>0.8799999999999999</x:v>
+      </x:c>
+      <x:c r="L12" s="21" t="str">
+        <x:v>{"answer":0.85,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="M12" s="118" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="F12" s="21" t="n">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="G12" s="111" t="str">
-        <x:v>{"answer":0.86,"unit":"V"}</x:v>
-      </x:c>
-      <x:c r="H12" s="21" t="n">
-        <x:v>0.933333</x:v>
-      </x:c>
-      <x:c r="I12" s="24" t="n">
-        <x:v>0.9199999999999999</x:v>
-      </x:c>
-      <x:c r="J12" s="114" t="str">
-        <x:v>{"answer":0.88,"unit":"V"}</x:v>
-      </x:c>
-      <x:c r="K12" s="24" t="n">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="L12" s="21" t="n">
-        <x:v>0.8799999999999999</x:v>
-      </x:c>
-      <x:c r="M12" s="118" t="str">
-        <x:v>{"answer":0.85,"unit":"V"}</x:v>
-      </x:c>
       <x:c r="N12" s="120" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="O12" s="122" t="n">
         <x:v>0.94</x:v>
       </x:c>
     </x:row>
@@ -1456,42 +1426,39 @@
         <x:v>{"answer":1.11,"unit":"V"}</x:v>
       </x:c>
       <x:c r="C13" s="99" t="str">
-        <x:v>first_oxidation_potential_vs_sce：标准答案 1.11 V；版本 linear_goal_v2。满分：x=1.11 V。部分分：0.51 &lt; x &lt; 1.11 或 1.11 &lt; x &lt; 1.71（按绝对误差线性递减）。0分：x &lt;= 0.51 或 x &gt;= 1.71；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D13" s="99" t="str">
         <x:v>{"answer":0.86,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="D13" s="99" t="n">
+        <x:v>0.583333</x:v>
+      </x:c>
       <x:c r="E13" s="24" t="n">
-        <x:v>0.583333</x:v>
-      </x:c>
-      <x:c r="F13" s="21" t="n">
         <x:v>0.4999999999999998</x:v>
       </x:c>
-      <x:c r="G13" s="111" t="str">
+      <x:c r="F13" s="21" t="str">
         <x:v>{"answer":0.93,"unit":"V"}</x:v>
       </x:c>
+      <x:c r="G13" s="111" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
       <x:c r="H13" s="21" t="n">
+        <x:v>0.6399999999999999</x:v>
+      </x:c>
+      <x:c r="I13" s="24" t="str">
+        <x:v>{"answer":1.06,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="J13" s="114" t="n">
+        <x:v>0.916667</x:v>
+      </x:c>
+      <x:c r="K13" s="24" t="n">
+        <x:v>0.8999999999999999</x:v>
+      </x:c>
+      <x:c r="L13" s="21" t="str">
+        <x:v>{"answer":0.93,"unit":"V"}</x:v>
+      </x:c>
+      <x:c r="M13" s="118" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="I13" s="24" t="n">
-        <x:v>0.6399999999999999</x:v>
-      </x:c>
-      <x:c r="J13" s="114" t="str">
-        <x:v>{"answer":1.06,"unit":"V"}</x:v>
-      </x:c>
-      <x:c r="K13" s="24" t="n">
-        <x:v>0.916667</x:v>
-      </x:c>
-      <x:c r="L13" s="21" t="n">
-        <x:v>0.8999999999999999</x:v>
-      </x:c>
-      <x:c r="M13" s="118" t="str">
-        <x:v>{"answer":0.93,"unit":"V"}</x:v>
-      </x:c>
       <x:c r="N13" s="120" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="O13" s="122" t="n">
         <x:v>0.6399999999999999</x:v>
       </x:c>
     </x:row>
@@ -1503,42 +1470,39 @@
         <x:v>{"answer":-4.97,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C14" s="99" t="str">
-        <x:v>binding_energy：标准答案 -4.97 kcal/mol；版本 linear_goal_v2。满分：x=-4.97 kcal/mol。部分分：-7.97 &lt; x &lt; -4.97 或 -4.97 &lt; x &lt; -1.97（按绝对误差线性递减）。0分：x &lt;= -7.97 或 x &gt;= -1.97；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D14" s="99" t="str">
         <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D14" s="99" t="n">
+        <x:v>0.983333</x:v>
+      </x:c>
       <x:c r="E14" s="24" t="n">
+        <x:v>0.9500000000000002</x:v>
+      </x:c>
+      <x:c r="F14" s="21" t="str">
+        <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="G14" s="111" t="n">
         <x:v>0.983333</x:v>
       </x:c>
-      <x:c r="F14" s="21" t="n">
+      <x:c r="H14" s="21" t="n">
         <x:v>0.9500000000000002</x:v>
       </x:c>
-      <x:c r="G14" s="111" t="str">
-        <x:v>{"answer":-5.02,"unit":"kcal/mol"}</x:v>
-      </x:c>
-      <x:c r="H14" s="21" t="n">
-        <x:v>0.983333</x:v>
-      </x:c>
-      <x:c r="I14" s="24" t="n">
-        <x:v>0.9500000000000002</x:v>
-      </x:c>
-      <x:c r="J14" s="114" t="str">
+      <x:c r="I14" s="24" t="str">
         <x:v>{"answer":-4.4,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J14" s="114" t="n">
+        <x:v>0.81</x:v>
+      </x:c>
       <x:c r="K14" s="24" t="n">
-        <x:v>0.81</x:v>
-      </x:c>
-      <x:c r="L14" s="21" t="n">
         <x:v>0.4300000000000006</x:v>
       </x:c>
-      <x:c r="M14" s="118" t="str">
+      <x:c r="L14" s="21" t="str">
         <x:v>{"answer":-5.0,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M14" s="118" t="n">
+        <x:v>0.99</x:v>
+      </x:c>
       <x:c r="N14" s="120" t="n">
-        <x:v>0.99</x:v>
-      </x:c>
-      <x:c r="O14" s="122" t="n">
         <x:v>0.9699999999999998</x:v>
       </x:c>
     </x:row>
@@ -1550,42 +1514,39 @@
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C15" s="99" t="str">
-        <x:v>binding_energy：标准答案 -2.85 kcal/mol；版本 linear_goal_v2。满分：x=-2.85 kcal/mol。部分分：-5.85 &lt; x &lt; -2.85 或 -2.85 &lt; x &lt; 0.15（按绝对误差线性递减）。0分：x &lt;= -5.85 或 x &gt;= 0.15；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D15" s="99" t="str">
         <x:v>{"answer":-1.7621272831,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D15" s="99" t="n">
+        <x:v>0.637376</x:v>
+      </x:c>
       <x:c r="E15" s="24" t="n">
-        <x:v>0.637376</x:v>
-      </x:c>
-      <x:c r="F15" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="111" t="str">
+      <x:c r="F15" s="21" t="str">
         <x:v>{"answer":-3.17,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G15" s="111" t="n">
+        <x:v>0.893333</x:v>
+      </x:c>
       <x:c r="H15" s="21" t="n">
-        <x:v>0.893333</x:v>
-      </x:c>
-      <x:c r="I15" s="24" t="n">
         <x:v>0.6800000000000002</x:v>
       </x:c>
-      <x:c r="J15" s="114" t="str">
+      <x:c r="I15" s="24" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J15" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L15" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M15" s="118" t="str">
+      <x:c r="L15" s="21" t="str">
         <x:v>{"answer":-2.85,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M15" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N15" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1597,42 +1558,39 @@
         <x:v>{"answer":-2.48,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C16" s="99" t="str">
-        <x:v>binding_energy：标准答案 -2.48 kcal/mol；版本 linear_goal_v2。满分：x=-2.48 kcal/mol。部分分：-5.48 &lt; x &lt; -2.48 或 -2.48 &lt; x &lt; 0.52（按绝对误差线性递减）。0分：x &lt;= -5.48 或 x &gt;= 0.52；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D16" s="99" t="str">
         <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D16" s="99" t="n">
+        <x:v>0.913333</x:v>
+      </x:c>
       <x:c r="E16" s="24" t="n">
+        <x:v>0.7399999999999998</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="str">
+        <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="G16" s="111" t="n">
         <x:v>0.913333</x:v>
       </x:c>
-      <x:c r="F16" s="21" t="n">
+      <x:c r="H16" s="21" t="n">
         <x:v>0.7399999999999998</x:v>
       </x:c>
-      <x:c r="G16" s="111" t="str">
-        <x:v>{"answer":-2.74,"unit":"kcal/mol"}</x:v>
-      </x:c>
-      <x:c r="H16" s="21" t="n">
-        <x:v>0.913333</x:v>
-      </x:c>
-      <x:c r="I16" s="24" t="n">
-        <x:v>0.7399999999999998</x:v>
-      </x:c>
-      <x:c r="J16" s="114" t="str">
+      <x:c r="I16" s="24" t="str">
         <x:v>{"answer":-2.25,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J16" s="114" t="n">
+        <x:v>0.923333</x:v>
+      </x:c>
       <x:c r="K16" s="24" t="n">
-        <x:v>0.923333</x:v>
-      </x:c>
-      <x:c r="L16" s="21" t="n">
         <x:v>0.77</x:v>
       </x:c>
-      <x:c r="M16" s="118" t="str">
+      <x:c r="L16" s="21" t="str">
         <x:v>{"answer":-2.4,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M16" s="118" t="n">
+        <x:v>0.973333</x:v>
+      </x:c>
       <x:c r="N16" s="120" t="n">
-        <x:v>0.973333</x:v>
-      </x:c>
-      <x:c r="O16" s="122" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
     </x:row>
@@ -1644,42 +1602,39 @@
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C17" s="99" t="str">
-        <x:v>binding_energy：标准答案 -16.13 kcal/mol；版本 linear_goal_v2。满分：x=-16.13 kcal/mol。部分分：-19.13 &lt; x &lt; -16.13 或 -16.13 &lt; x &lt; -13.13（按绝对误差线性递减）。0分：x &lt;= -19.13 或 x &gt;= -13.13；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D17" s="99" t="str">
         <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D17" s="99" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
       <x:c r="E17" s="24" t="n">
+        <x:v>0.759999999999998</x:v>
+      </x:c>
+      <x:c r="F17" s="21" t="str">
+        <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="G17" s="111" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="F17" s="21" t="n">
+      <x:c r="H17" s="21" t="n">
         <x:v>0.759999999999998</x:v>
       </x:c>
-      <x:c r="G17" s="111" t="str">
-        <x:v>{"answer":-16.37,"unit":"kcal/mol"}</x:v>
-      </x:c>
-      <x:c r="H17" s="21" t="n">
-        <x:v>0.92</x:v>
-      </x:c>
-      <x:c r="I17" s="24" t="n">
-        <x:v>0.759999999999998</x:v>
-      </x:c>
-      <x:c r="J17" s="114" t="str">
+      <x:c r="I17" s="24" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J17" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L17" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M17" s="118" t="str">
+      <x:c r="L17" s="21" t="str">
         <x:v>{"answer":-16.47,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M17" s="118" t="n">
+        <x:v>0.886667</x:v>
+      </x:c>
       <x:c r="N17" s="120" t="n">
-        <x:v>0.886667</x:v>
-      </x:c>
-      <x:c r="O17" s="122" t="n">
         <x:v>0.6600000000000001</x:v>
       </x:c>
     </x:row>
@@ -1691,42 +1646,39 @@
         <x:v>{"answer":-4.89,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C18" s="99" t="str">
-        <x:v>binding_energy：标准答案 -4.89 kcal/mol；版本 linear_goal_v2。满分：x=-4.89 kcal/mol。部分分：-7.89 &lt; x &lt; -4.89 或 -4.89 &lt; x &lt; -1.89（按绝对误差线性递减）。0分：x &lt;= -7.89 或 x &gt;= -1.89；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D18" s="99" t="str">
         <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D18" s="99" t="n">
+        <x:v>0.926667</x:v>
+      </x:c>
       <x:c r="E18" s="24" t="n">
+        <x:v>0.7799999999999994</x:v>
+      </x:c>
+      <x:c r="F18" s="21" t="str">
+        <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
+      </x:c>
+      <x:c r="G18" s="111" t="n">
         <x:v>0.926667</x:v>
       </x:c>
-      <x:c r="F18" s="21" t="n">
+      <x:c r="H18" s="21" t="n">
         <x:v>0.7799999999999994</x:v>
       </x:c>
-      <x:c r="G18" s="111" t="str">
-        <x:v>{"answer":-5.11,"unit":"kcal/mol"}</x:v>
-      </x:c>
-      <x:c r="H18" s="21" t="n">
-        <x:v>0.926667</x:v>
-      </x:c>
-      <x:c r="I18" s="24" t="n">
-        <x:v>0.7799999999999994</x:v>
-      </x:c>
-      <x:c r="J18" s="114" t="str">
+      <x:c r="I18" s="24" t="str">
         <x:v>{"answer":-4.87,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J18" s="114" t="n">
+        <x:v>0.993333</x:v>
+      </x:c>
       <x:c r="K18" s="24" t="n">
-        <x:v>0.993333</x:v>
-      </x:c>
-      <x:c r="L18" s="21" t="n">
         <x:v>0.9800000000000004</x:v>
       </x:c>
-      <x:c r="M18" s="118" t="str">
+      <x:c r="L18" s="21" t="str">
         <x:v>{"answer":-4.96,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M18" s="118" t="n">
+        <x:v>0.976667</x:v>
+      </x:c>
       <x:c r="N18" s="120" t="n">
-        <x:v>0.976667</x:v>
-      </x:c>
-      <x:c r="O18" s="122" t="n">
         <x:v>0.9299999999999997</x:v>
       </x:c>
     </x:row>
@@ -1738,42 +1690,39 @@
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C19" s="99" t="str">
-        <x:v>binding_energy：标准答案 -1.33 kcal/mol；版本 linear_goal_v2。满分：x=-1.33 kcal/mol。部分分：-4.33 &lt; x &lt; -1.33 或 -1.33 &lt; x &lt; 1.67（按绝对误差线性递减）。0分：x &lt;= -4.33 或 x &gt;= 1.67；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D19" s="99" t="str">
         <x:v>{"answer":0.784,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D19" s="99" t="n">
+        <x:v>0.295333</x:v>
+      </x:c>
       <x:c r="E19" s="24" t="n">
-        <x:v>0.295333</x:v>
-      </x:c>
-      <x:c r="F19" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="111" t="str">
+      <x:c r="F19" s="21" t="str">
         <x:v>{"answer":-1.53,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G19" s="111" t="n">
+        <x:v>0.933333</x:v>
+      </x:c>
       <x:c r="H19" s="21" t="n">
-        <x:v>0.933333</x:v>
-      </x:c>
-      <x:c r="I19" s="24" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="J19" s="114" t="str">
+      <x:c r="I19" s="24" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J19" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K19" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L19" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M19" s="118" t="str">
+      <x:c r="L19" s="21" t="str">
         <x:v>{"answer":-1.33,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M19" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N19" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1785,42 +1734,39 @@
         <x:v>{"answer":65.01,"unit":"a.u."}</x:v>
       </x:c>
       <x:c r="C20" s="99" t="str">
-        <x:v>static_mean_polarizability：标准答案 65.01 a.u.；版本 linear_goal_v2。满分：x=65.01 a.u.。部分分：相对误差小于 25% 按距离线性递减。0分：相对误差大于等于 25%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D20" s="99" t="str">
         <x:v>{"answer":65.014425,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="D20" s="99" t="n">
+        <x:v>0.999728</x:v>
+      </x:c>
       <x:c r="E20" s="24" t="n">
+        <x:v>0.9996596677434243</x:v>
+      </x:c>
+      <x:c r="F20" s="21" t="str">
+        <x:v>{"answer":65.014427,"unit":"a.u."}</x:v>
+      </x:c>
+      <x:c r="G20" s="111" t="n">
         <x:v>0.999728</x:v>
       </x:c>
-      <x:c r="F20" s="21" t="n">
-        <x:v>0.9996596677434243</x:v>
-      </x:c>
-      <x:c r="G20" s="111" t="str">
-        <x:v>{"answer":65.014427,"unit":"a.u."}</x:v>
-      </x:c>
       <x:c r="H20" s="21" t="n">
-        <x:v>0.999728</x:v>
-      </x:c>
-      <x:c r="I20" s="24" t="n">
         <x:v>0.9996595139209358</x:v>
       </x:c>
-      <x:c r="J20" s="114" t="str">
+      <x:c r="I20" s="24" t="str">
         <x:v>{"answer":65.0135,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="J20" s="114" t="n">
+        <x:v>0.999785</x:v>
+      </x:c>
       <x:c r="K20" s="24" t="n">
-        <x:v>0.999785</x:v>
-      </x:c>
-      <x:c r="L20" s="21" t="n">
         <x:v>0.9997308106445171</x:v>
       </x:c>
-      <x:c r="M20" s="118" t="str">
+      <x:c r="L20" s="21" t="str">
         <x:v>{"answer":65.014,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="M20" s="118" t="n">
+        <x:v>0.999754</x:v>
+      </x:c>
       <x:c r="N20" s="120" t="n">
-        <x:v>0.999754</x:v>
-      </x:c>
-      <x:c r="O20" s="122" t="n">
         <x:v>0.999692355022305</x:v>
       </x:c>
     </x:row>
@@ -1832,42 +1778,39 @@
         <x:v>{"answer":67.87,"unit":"a.u."}</x:v>
       </x:c>
       <x:c r="C21" s="99" t="str">
-        <x:v>static_mean_polarizability：标准答案 67.87 a.u.；版本 linear_goal_v2。满分：x=67.87 a.u.。部分分：相对误差小于 25% 按距离线性递减。0分：相对误差大于等于 25%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D21" s="99" t="str">
         <x:v>{"answer":58.9073,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="D21" s="99" t="n">
+        <x:v>0.471773</x:v>
+      </x:c>
       <x:c r="E21" s="24" t="n">
-        <x:v>0.471773</x:v>
-      </x:c>
-      <x:c r="F21" s="21" t="n">
         <x:v>0.33971563282746386</x:v>
       </x:c>
-      <x:c r="G21" s="111" t="str">
+      <x:c r="F21" s="21" t="str">
         <x:v>{"answer":67.869889,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="G21" s="111" t="n">
+        <x:v>0.999993</x:v>
+      </x:c>
       <x:c r="H21" s="21" t="n">
-        <x:v>0.999993</x:v>
-      </x:c>
-      <x:c r="I21" s="24" t="n">
         <x:v>0.999991822602033</x:v>
       </x:c>
-      <x:c r="J21" s="114" t="str">
+      <x:c r="I21" s="24" t="str">
         <x:v>{"answer":67.8696,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="J21" s="114" t="n">
+        <x:v>0.999976</x:v>
+      </x:c>
       <x:c r="K21" s="24" t="n">
-        <x:v>0.999976</x:v>
-      </x:c>
-      <x:c r="L21" s="21" t="n">
         <x:v>0.9999705318992191</x:v>
       </x:c>
-      <x:c r="M21" s="118" t="str">
+      <x:c r="L21" s="21" t="str">
         <x:v>{"answer":67.87,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="M21" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N21" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1879,42 +1822,39 @@
         <x:v>{"answer":95.51,"unit":"a.u."}</x:v>
       </x:c>
       <x:c r="C22" s="99" t="str">
-        <x:v>static_mean_polarizability：标准答案 95.51 a.u.；版本 linear_goal_v2。满分：x=95.51 a.u.。部分分：相对误差小于 25% 按距离线性递减。0分：相对误差大于等于 25%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D22" s="99" t="str">
         <x:v>{"answer":95.508492,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="D22" s="99" t="n">
+        <x:v>0.999937</x:v>
+      </x:c>
       <x:c r="E22" s="24" t="n">
-        <x:v>0.999937</x:v>
-      </x:c>
-      <x:c r="F22" s="21" t="n">
         <x:v>0.9999210553868704</x:v>
       </x:c>
-      <x:c r="G22" s="111" t="str">
+      <x:c r="F22" s="21" t="str">
         <x:v>{"answer":95.531814,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="G22" s="111" t="n">
+        <x:v>0.999086</x:v>
+      </x:c>
       <x:c r="H22" s="21" t="n">
-        <x:v>0.999086</x:v>
-      </x:c>
-      <x:c r="I22" s="24" t="n">
         <x:v>0.9988580253376614</x:v>
       </x:c>
-      <x:c r="J22" s="114" t="str">
+      <x:c r="I22" s="24" t="str">
         <x:v>{"answer":101.7,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="J22" s="114" t="n">
+        <x:v>0.74076</x:v>
+      </x:c>
       <x:c r="K22" s="24" t="n">
-        <x:v>0.74076</x:v>
-      </x:c>
-      <x:c r="L22" s="21" t="n">
         <x:v>0.6759501622866717</x:v>
       </x:c>
-      <x:c r="M22" s="118" t="str">
+      <x:c r="L22" s="21" t="str">
         <x:v>{"answer":95.51,"unit":"a.u."}</x:v>
       </x:c>
+      <x:c r="M22" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N22" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1926,42 +1866,39 @@
         <x:v>{"answer":5.43,"unit":"Debye"}</x:v>
       </x:c>
       <x:c r="C23" s="99" t="str">
-        <x:v>dipole_moment：标准答案 5.43 Debye；版本 linear_goal_v2。满分：x=5.43 Debye。部分分：相对误差小于 35% 按距离线性递减。0分：相对误差大于等于 35%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D23" s="99" t="str">
         <x:v>{"answer":5.430,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="D23" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E23" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G23" s="111" t="str">
+      <x:c r="F23" s="21" t="str">
         <x:v>{"answer":5.431,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="G23" s="111" t="n">
+        <x:v>0.999474</x:v>
+      </x:c>
       <x:c r="H23" s="21" t="n">
-        <x:v>0.999474</x:v>
-      </x:c>
-      <x:c r="I23" s="24" t="n">
         <x:v>0.9990791896869242</x:v>
       </x:c>
-      <x:c r="J23" s="114" t="str">
+      <x:c r="I23" s="24" t="str">
         <x:v>{"answer":5.433,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="J23" s="114" t="n">
+        <x:v>0.998421</x:v>
+      </x:c>
       <x:c r="K23" s="24" t="n">
-        <x:v>0.998421</x:v>
-      </x:c>
-      <x:c r="L23" s="21" t="n">
         <x:v>0.9972375690607733</x:v>
       </x:c>
-      <x:c r="M23" s="118" t="str">
+      <x:c r="L23" s="21" t="str">
         <x:v>{"answer":5.434,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="M23" s="118" t="n">
+        <x:v>0.997895</x:v>
+      </x:c>
       <x:c r="N23" s="120" t="n">
-        <x:v>0.997895</x:v>
-      </x:c>
-      <x:c r="O23" s="122" t="n">
         <x:v>0.9963167587476975</x:v>
       </x:c>
     </x:row>
@@ -1973,42 +1910,39 @@
         <x:v>{"answer":1.88,"unit":"Debye"}</x:v>
       </x:c>
       <x:c r="C24" s="99" t="str">
-        <x:v>dipole_moment：标准答案 1.88 Debye；版本 linear_goal_v2。满分：x=1.88 Debye。部分分：相对误差小于 35% 按距离线性递减。0分：相对误差大于等于 35%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D24" s="99" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="D24" s="99" t="n">
+        <x:v>0.99696</x:v>
+      </x:c>
       <x:c r="E24" s="24" t="n">
+        <x:v>0.9946808510638298</x:v>
+      </x:c>
+      <x:c r="F24" s="21" t="str">
+        <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
+      </x:c>
+      <x:c r="G24" s="111" t="n">
         <x:v>0.99696</x:v>
       </x:c>
-      <x:c r="F24" s="21" t="n">
+      <x:c r="H24" s="21" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
-      <x:c r="G24" s="111" t="str">
+      <x:c r="I24" s="24" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="H24" s="21" t="n">
+      <x:c r="J24" s="114" t="n">
         <x:v>0.99696</x:v>
       </x:c>
-      <x:c r="I24" s="24" t="n">
+      <x:c r="K24" s="24" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
-      <x:c r="J24" s="114" t="str">
+      <x:c r="L24" s="21" t="str">
         <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
       </x:c>
-      <x:c r="K24" s="24" t="n">
+      <x:c r="M24" s="118" t="n">
         <x:v>0.99696</x:v>
       </x:c>
-      <x:c r="L24" s="21" t="n">
-        <x:v>0.9946808510638298</x:v>
-      </x:c>
-      <x:c r="M24" s="118" t="str">
-        <x:v>{"answer":1.882,"unit":"Debye"}</x:v>
-      </x:c>
       <x:c r="N24" s="120" t="n">
-        <x:v>0.99696</x:v>
-      </x:c>
-      <x:c r="O24" s="122" t="n">
         <x:v>0.9946808510638298</x:v>
       </x:c>
     </x:row>
@@ -2020,42 +1954,39 @@
         <x:v>{"answer":3.85,"unit":"Debye"}</x:v>
       </x:c>
       <x:c r="C25" s="99" t="str">
-        <x:v>dipole_moment：标准答案 3.85 Debye；版本 linear_goal_v2。满分：x=3.85 Debye。部分分：相对误差小于 35% 按距离线性递减。0分：相对误差大于等于 35%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D25" s="99" t="str">
         <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="D25" s="99" t="n">
+        <x:v>0.998516</x:v>
+      </x:c>
       <x:c r="E25" s="24" t="n">
+        <x:v>0.9974025974025977</x:v>
+      </x:c>
+      <x:c r="F25" s="21" t="str">
+        <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
+      </x:c>
+      <x:c r="G25" s="111" t="n">
         <x:v>0.998516</x:v>
       </x:c>
-      <x:c r="F25" s="21" t="n">
+      <x:c r="H25" s="21" t="n">
         <x:v>0.9974025974025977</x:v>
       </x:c>
-      <x:c r="G25" s="111" t="str">
-        <x:v>{"answer":3.852,"unit":"Debye"}</x:v>
-      </x:c>
-      <x:c r="H25" s="21" t="n">
-        <x:v>0.998516</x:v>
-      </x:c>
-      <x:c r="I25" s="24" t="n">
-        <x:v>0.9974025974025977</x:v>
-      </x:c>
-      <x:c r="J25" s="114" t="str">
+      <x:c r="I25" s="24" t="str">
         <x:v>{"answer":3.851,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="J25" s="114" t="n">
+        <x:v>0.999258</x:v>
+      </x:c>
       <x:c r="K25" s="24" t="n">
-        <x:v>0.999258</x:v>
-      </x:c>
-      <x:c r="L25" s="21" t="n">
         <x:v>0.9987012987012989</x:v>
       </x:c>
-      <x:c r="M25" s="118" t="str">
+      <x:c r="L25" s="21" t="str">
         <x:v>{"answer":3.85,"unit":"Debye"}</x:v>
       </x:c>
+      <x:c r="M25" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N25" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2067,42 +1998,39 @@
         <x:v>{"answer":1.2522,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C26" s="99" t="str">
-        <x:v>wiberg_bond_order：标准答案 1.2522 dimensionless；版本 linear_goal_v2。满分：x=1.2522 dimensionless。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D26" s="99" t="str">
         <x:v>{"answer":1.252,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D26" s="99" t="n">
+        <x:v>0.999201</x:v>
+      </x:c>
       <x:c r="E26" s="24" t="n">
-        <x:v>0.999201</x:v>
-      </x:c>
-      <x:c r="F26" s="21" t="n">
         <x:v>0.9990000000000001</x:v>
       </x:c>
-      <x:c r="G26" s="111" t="str">
+      <x:c r="F26" s="21" t="str">
         <x:v>{"answer":1.2522024,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G26" s="111" t="n">
+        <x:v>0.99999</x:v>
+      </x:c>
       <x:c r="H26" s="21" t="n">
-        <x:v>0.99999</x:v>
-      </x:c>
-      <x:c r="I26" s="24" t="n">
         <x:v>0.9999879999999997</x:v>
       </x:c>
-      <x:c r="J26" s="114" t="str">
+      <x:c r="I26" s="24" t="str">
         <x:v>{"answer":1.2522,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J26" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K26" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L26" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M26" s="118" t="str">
+      <x:c r="L26" s="21" t="str">
         <x:v>{"answer":1.2523,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="M26" s="118" t="n">
+        <x:v>0.999601</x:v>
+      </x:c>
       <x:c r="N26" s="120" t="n">
-        <x:v>0.999601</x:v>
-      </x:c>
-      <x:c r="O26" s="122" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
@@ -2114,42 +2042,39 @@
         <x:v>{"answer":1.6615,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C27" s="99" t="str">
-        <x:v>wiberg_bond_order：标准答案 1.6615 dimensionless；版本 linear_goal_v2。满分：x=1.6615 dimensionless。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D27" s="99" t="str">
         <x:v>{"answer":1.639,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D27" s="99" t="n">
+        <x:v>0.93229</x:v>
+      </x:c>
       <x:c r="E27" s="24" t="n">
-        <x:v>0.93229</x:v>
-      </x:c>
-      <x:c r="F27" s="21" t="n">
         <x:v>0.8875000000000002</x:v>
       </x:c>
-      <x:c r="G27" s="111" t="str">
+      <x:c r="F27" s="21" t="str">
         <x:v>{"answer":1.6615304058,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G27" s="111" t="n">
+        <x:v>0.999908</x:v>
+      </x:c>
       <x:c r="H27" s="21" t="n">
-        <x:v>0.999908</x:v>
-      </x:c>
-      <x:c r="I27" s="24" t="n">
         <x:v>0.9998479709999999</x:v>
       </x:c>
-      <x:c r="J27" s="114" t="str">
+      <x:c r="I27" s="24" t="str">
         <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J27" s="114" t="n">
+        <x:v>0.999699</x:v>
+      </x:c>
       <x:c r="K27" s="24" t="n">
+        <x:v>0.9995</x:v>
+      </x:c>
+      <x:c r="L27" s="21" t="str">
+        <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="M27" s="118" t="n">
         <x:v>0.999699</x:v>
       </x:c>
-      <x:c r="L27" s="21" t="n">
-        <x:v>0.9995</x:v>
-      </x:c>
-      <x:c r="M27" s="118" t="str">
-        <x:v>{"answer":1.6614,"unit":"dimensionless"}</x:v>
-      </x:c>
       <x:c r="N27" s="120" t="n">
-        <x:v>0.999699</x:v>
-      </x:c>
-      <x:c r="O27" s="122" t="n">
         <x:v>0.9995</x:v>
       </x:c>
     </x:row>
@@ -2161,42 +2086,39 @@
         <x:v>{"answer":0.9292,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C28" s="99" t="str">
-        <x:v>wiberg_bond_order：标准答案 0.9292 dimensionless；版本 linear_goal_v2。满分：x=0.9292 dimensionless。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D28" s="99" t="str">
         <x:v>{"answer":0.930,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D28" s="99" t="n">
+        <x:v>0.995695</x:v>
+      </x:c>
       <x:c r="E28" s="24" t="n">
+        <x:v>0.9959999999999999</x:v>
+      </x:c>
+      <x:c r="F28" s="21" t="str">
+        <x:v>{"answer":0.9661815181817287,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="G28" s="111" t="n">
+        <x:v>0.801003</x:v>
+      </x:c>
+      <x:c r="H28" s="21" t="n">
+        <x:v>0.8150924090913566</x:v>
+      </x:c>
+      <x:c r="I28" s="24" t="str">
+        <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="J28" s="114" t="n">
         <x:v>0.995695</x:v>
       </x:c>
-      <x:c r="F28" s="21" t="n">
+      <x:c r="K28" s="24" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
-      <x:c r="G28" s="111" t="str">
-        <x:v>{"answer":0.9661815181817287,"unit":"dimensionless"}</x:v>
-      </x:c>
-      <x:c r="H28" s="21" t="n">
-        <x:v>0.801003</x:v>
-      </x:c>
-      <x:c r="I28" s="24" t="n">
-        <x:v>0.8150924090913566</x:v>
-      </x:c>
-      <x:c r="J28" s="114" t="str">
+      <x:c r="L28" s="21" t="str">
         <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
       </x:c>
-      <x:c r="K28" s="24" t="n">
+      <x:c r="M28" s="118" t="n">
         <x:v>0.995695</x:v>
       </x:c>
-      <x:c r="L28" s="21" t="n">
-        <x:v>0.9959999999999999</x:v>
-      </x:c>
-      <x:c r="M28" s="118" t="str">
-        <x:v>{"answer":0.93,"unit":"dimensionless"}</x:v>
-      </x:c>
       <x:c r="N28" s="120" t="n">
-        <x:v>0.995695</x:v>
-      </x:c>
-      <x:c r="O28" s="122" t="n">
         <x:v>0.9959999999999999</x:v>
       </x:c>
     </x:row>
@@ -2208,42 +2130,39 @@
         <x:v>{"answer":-25.95,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C29" s="99" t="str">
-        <x:v>surface_electrostatic_potential_minimum：标准答案 -25.95 kcal/mol；版本 linear_goal_v2。满分：x=-25.95 kcal/mol。部分分：相对误差小于 40% 按距离线性递减。0分：相对误差大于等于 40%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D29" s="99" t="str">
         <x:v>{"answer":-32.7295,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D29" s="99" t="n">
+        <x:v>0.346869</x:v>
+      </x:c>
       <x:c r="E29" s="24" t="n">
-        <x:v>0.346869</x:v>
-      </x:c>
-      <x:c r="F29" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="111" t="str">
+      <x:c r="F29" s="21" t="str">
         <x:v>{"answer":-26.0378553128,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G29" s="111" t="n">
+        <x:v>0.991536</x:v>
+      </x:c>
       <x:c r="H29" s="21" t="n">
-        <x:v>0.991536</x:v>
-      </x:c>
-      <x:c r="I29" s="24" t="n">
         <x:v>0.9824289374399996</x:v>
       </x:c>
-      <x:c r="J29" s="114" t="str">
+      <x:c r="I29" s="24" t="str">
         <x:v>{"answer":-26.0,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J29" s="114" t="n">
+        <x:v>0.995183</x:v>
+      </x:c>
       <x:c r="K29" s="24" t="n">
-        <x:v>0.995183</x:v>
-      </x:c>
-      <x:c r="L29" s="21" t="n">
         <x:v>0.9899999999999999</x:v>
       </x:c>
-      <x:c r="M29" s="118" t="str">
+      <x:c r="L29" s="21" t="str">
         <x:v>{"answer":-32.74,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M29" s="118" t="n">
+        <x:v>0.345857</x:v>
+      </x:c>
       <x:c r="N29" s="120" t="n">
-        <x:v>0.345857</x:v>
-      </x:c>
-      <x:c r="O29" s="122" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2255,42 +2174,39 @@
         <x:v>{"answer":150.3,"unit":"angstrom^2"}</x:v>
       </x:c>
       <x:c r="C30" s="99" t="str">
-        <x:v>van_der_waals_surface_area：标准答案 150.3 angstrom^2；版本 linear_goal_v2。满分：x=150.3 angstrom^2。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D30" s="99" t="str">
         <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
       </x:c>
+      <x:c r="D30" s="99" t="n">
+        <x:v>0.999335</x:v>
+      </x:c>
       <x:c r="E30" s="24" t="n">
+        <x:v>0.9986693280106466</x:v>
+      </x:c>
+      <x:c r="F30" s="21" t="str">
+        <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
+      </x:c>
+      <x:c r="G30" s="111" t="n">
         <x:v>0.999335</x:v>
       </x:c>
-      <x:c r="F30" s="21" t="n">
+      <x:c r="H30" s="21" t="n">
         <x:v>0.9986693280106466</x:v>
       </x:c>
-      <x:c r="G30" s="111" t="str">
-        <x:v>{"answer":150.32,"unit":"angstrom^2"}</x:v>
-      </x:c>
-      <x:c r="H30" s="21" t="n">
-        <x:v>0.999335</x:v>
-      </x:c>
-      <x:c r="I30" s="24" t="n">
-        <x:v>0.9986693280106466</x:v>
-      </x:c>
-      <x:c r="J30" s="114" t="str">
+      <x:c r="I30" s="24" t="str">
         <x:v>{"answer":137.5,"unit":"angstrom^2"}</x:v>
       </x:c>
+      <x:c r="J30" s="114" t="n">
+        <x:v>0.574185</x:v>
+      </x:c>
       <x:c r="K30" s="24" t="n">
-        <x:v>0.574185</x:v>
-      </x:c>
-      <x:c r="L30" s="21" t="n">
         <x:v>0.14836992681303984</x:v>
       </x:c>
-      <x:c r="M30" s="118" t="str">
+      <x:c r="L30" s="21" t="str">
         <x:v>{"answer":135.4,"unit":"angstrom^2"}</x:v>
       </x:c>
+      <x:c r="M30" s="118" t="n">
+        <x:v>0.504325</x:v>
+      </x:c>
       <x:c r="N30" s="120" t="n">
-        <x:v>0.504325</x:v>
-      </x:c>
-      <x:c r="O30" s="122" t="n">
         <x:v>0.008649367930804619</x:v>
       </x:c>
     </x:row>
@@ -2302,42 +2218,39 @@
         <x:v>{"answer":178.25,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
       <x:c r="C31" s="99" t="str">
-        <x:v>surface_electrostatic_potential_total_variance：标准答案 178.25 (kcal/mol)^2；版本 linear_goal_v2。满分：x=178.25 (kcal/mol)^2。部分分：相对误差小于 35% 按距离线性递减。0分：相对误差大于等于 35%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D31" s="99" t="str">
         <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
+      <x:c r="D31" s="99" t="n">
+        <x:v>0.975957</x:v>
+      </x:c>
       <x:c r="E31" s="24" t="n">
+        <x:v>0.9719495091164095</x:v>
+      </x:c>
+      <x:c r="F31" s="21" t="str">
+        <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
+      </x:c>
+      <x:c r="G31" s="111" t="n">
         <x:v>0.975957</x:v>
       </x:c>
-      <x:c r="F31" s="21" t="n">
+      <x:c r="H31" s="21" t="n">
         <x:v>0.9719495091164095</x:v>
       </x:c>
-      <x:c r="G31" s="111" t="str">
-        <x:v>{"answer":179.75,"unit":"(kcal/mol)^2"}</x:v>
-      </x:c>
-      <x:c r="H31" s="21" t="n">
-        <x:v>0.975957</x:v>
-      </x:c>
-      <x:c r="I31" s="24" t="n">
-        <x:v>0.9719495091164095</x:v>
-      </x:c>
-      <x:c r="J31" s="114" t="str">
+      <x:c r="I31" s="24" t="str">
         <x:v>{"answer":231.4,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
+      <x:c r="J31" s="114" t="n">
+        <x:v>0.148067</x:v>
+      </x:c>
       <x:c r="K31" s="24" t="n">
-        <x:v>0.148067</x:v>
-      </x:c>
-      <x:c r="L31" s="21" t="n">
         <x:v>0.006077606358111165</x:v>
       </x:c>
-      <x:c r="M31" s="118" t="str">
+      <x:c r="L31" s="21" t="str">
         <x:v>{"answer":323.6,"unit":"(kcal/mol)^2"}</x:v>
       </x:c>
+      <x:c r="M31" s="118" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N31" s="120" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O31" s="122" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2349,42 +2262,39 @@
         <x:v>{"answer":1.333,"unit":"g/cm^3"}</x:v>
       </x:c>
       <x:c r="C32" s="99" t="str">
-        <x:v>crystal_density：标准答案 1.333 g/cm^3；版本 linear_goal_v2。满分：x=1.333 g/cm^3。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D32" s="99" t="str">
         <x:v>{"answer":1.34923,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="D32" s="99" t="n">
+        <x:v>0.939122</x:v>
+      </x:c>
       <x:c r="E32" s="24" t="n">
-        <x:v>0.939122</x:v>
-      </x:c>
-      <x:c r="F32" s="21" t="n">
         <x:v>0.8782445611402854</x:v>
       </x:c>
-      <x:c r="G32" s="111" t="str">
+      <x:c r="F32" s="21" t="str">
         <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="G32" s="111" t="n">
+        <x:v>0.939985</x:v>
+      </x:c>
       <x:c r="H32" s="21" t="n">
+        <x:v>0.8799699924981245</x:v>
+      </x:c>
+      <x:c r="I32" s="24" t="str">
+        <x:v>{"answer":1.353,"unit":"g/cm^3"}</x:v>
+      </x:c>
+      <x:c r="J32" s="114" t="n">
+        <x:v>0.924981</x:v>
+      </x:c>
+      <x:c r="K32" s="24" t="n">
+        <x:v>0.8499624906226555</x:v>
+      </x:c>
+      <x:c r="L32" s="21" t="str">
+        <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
+      </x:c>
+      <x:c r="M32" s="118" t="n">
         <x:v>0.939985</x:v>
       </x:c>
-      <x:c r="I32" s="24" t="n">
-        <x:v>0.8799699924981245</x:v>
-      </x:c>
-      <x:c r="J32" s="114" t="str">
-        <x:v>{"answer":1.353,"unit":"g/cm^3"}</x:v>
-      </x:c>
-      <x:c r="K32" s="24" t="n">
-        <x:v>0.924981</x:v>
-      </x:c>
-      <x:c r="L32" s="21" t="n">
-        <x:v>0.8499624906226555</x:v>
-      </x:c>
-      <x:c r="M32" s="118" t="str">
-        <x:v>{"answer":1.349,"unit":"g/cm^3"}</x:v>
-      </x:c>
       <x:c r="N32" s="120" t="n">
-        <x:v>0.939985</x:v>
-      </x:c>
-      <x:c r="O32" s="122" t="n">
         <x:v>0.8799699924981245</x:v>
       </x:c>
     </x:row>
@@ -2396,42 +2306,39 @@
         <x:v>{"answer":1.71,"unit":"g/cm^3"}</x:v>
       </x:c>
       <x:c r="C33" s="99" t="str">
-        <x:v>crystal_density：标准答案 1.71 g/cm^3；版本 linear_goal_v2。满分：x=1.71 g/cm^3。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D33" s="99" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="D33" s="99" t="n">
+        <x:v>0.94152</x:v>
+      </x:c>
       <x:c r="E33" s="24" t="n">
+        <x:v>0.8830409356725145</x:v>
+      </x:c>
+      <x:c r="F33" s="21" t="str">
+        <x:v>{"answer":1.730,"unit":"g/cm^3"}</x:v>
+      </x:c>
+      <x:c r="G33" s="111" t="n">
         <x:v>0.94152</x:v>
       </x:c>
-      <x:c r="F33" s="21" t="n">
+      <x:c r="H33" s="21" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
-      <x:c r="G33" s="111" t="str">
-        <x:v>{"answer":1.730,"unit":"g/cm^3"}</x:v>
-      </x:c>
-      <x:c r="H33" s="21" t="n">
+      <x:c r="I33" s="24" t="str">
+        <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
+      </x:c>
+      <x:c r="J33" s="114" t="n">
         <x:v>0.94152</x:v>
       </x:c>
-      <x:c r="I33" s="24" t="n">
+      <x:c r="K33" s="24" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
-      <x:c r="J33" s="114" t="str">
+      <x:c r="L33" s="21" t="str">
         <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
       </x:c>
-      <x:c r="K33" s="24" t="n">
+      <x:c r="M33" s="118" t="n">
         <x:v>0.94152</x:v>
       </x:c>
-      <x:c r="L33" s="21" t="n">
-        <x:v>0.8830409356725145</x:v>
-      </x:c>
-      <x:c r="M33" s="118" t="str">
-        <x:v>{"answer":1.73,"unit":"g/cm^3"}</x:v>
-      </x:c>
       <x:c r="N33" s="120" t="n">
-        <x:v>0.94152</x:v>
-      </x:c>
-      <x:c r="O33" s="122" t="n">
         <x:v>0.8830409356725145</x:v>
       </x:c>
     </x:row>
@@ -2443,42 +2350,39 @@
         <x:v>{"answer":1.831,"unit":"g/cm^3"}</x:v>
       </x:c>
       <x:c r="C34" s="99" t="str">
-        <x:v>crystal_density：标准答案 1.831 g/cm^3；版本 linear_goal_v2。满分：x=1.831 g/cm^3。部分分：相对误差小于 20% 按距离线性递减。0分：相对误差大于等于 20%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D34" s="99" t="str">
         <x:v>{"answer":1.8508,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="D34" s="99" t="n">
+        <x:v>0.945931</x:v>
+      </x:c>
       <x:c r="E34" s="24" t="n">
-        <x:v>0.945931</x:v>
-      </x:c>
-      <x:c r="F34" s="21" t="n">
         <x:v>0.8918623702894591</x:v>
       </x:c>
-      <x:c r="G34" s="111" t="str">
+      <x:c r="F34" s="21" t="str">
         <x:v>{"answer":1.8527,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="G34" s="111" t="n">
+        <x:v>0.940743</x:v>
+      </x:c>
       <x:c r="H34" s="21" t="n">
-        <x:v>0.940743</x:v>
-      </x:c>
-      <x:c r="I34" s="24" t="n">
         <x:v>0.8814855270344072</x:v>
       </x:c>
-      <x:c r="J34" s="114" t="str">
+      <x:c r="I34" s="24" t="str">
         <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
       </x:c>
+      <x:c r="J34" s="114" t="n">
+        <x:v>0.939924</x:v>
+      </x:c>
       <x:c r="K34" s="24" t="n">
+        <x:v>0.8798470780993991</x:v>
+      </x:c>
+      <x:c r="L34" s="21" t="str">
+        <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
+      </x:c>
+      <x:c r="M34" s="118" t="n">
         <x:v>0.939924</x:v>
       </x:c>
-      <x:c r="L34" s="21" t="n">
-        <x:v>0.8798470780993991</x:v>
-      </x:c>
-      <x:c r="M34" s="118" t="str">
-        <x:v>{"answer":1.853,"unit":"g/cm^3"}</x:v>
-      </x:c>
       <x:c r="N34" s="120" t="n">
-        <x:v>0.939924</x:v>
-      </x:c>
-      <x:c r="O34" s="122" t="n">
         <x:v>0.8798470780993991</x:v>
       </x:c>
     </x:row>
@@ -2490,42 +2394,39 @@
         <x:v>{"answer":-0.266,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C35" s="99" t="str">
-        <x:v>spin_density：标准答案 -0.266 dimensionless；版本 linear_goal_v2。满分：x=-0.266 dimensionless。部分分：相对误差小于 80% 按距离线性递减。0分：相对误差大于等于 80%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D35" s="99" t="str">
         <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D35" s="99" t="n">
+        <x:v>0.958365</x:v>
+      </x:c>
       <x:c r="E35" s="24" t="n">
+        <x:v>0.9557000000000001</x:v>
+      </x:c>
+      <x:c r="F35" s="21" t="str">
+        <x:v>{"answer":-0.274885,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="G35" s="111" t="n">
+        <x:v>0.958247</x:v>
+      </x:c>
+      <x:c r="H35" s="21" t="n">
+        <x:v>0.9555750000000001</x:v>
+      </x:c>
+      <x:c r="I35" s="24" t="str">
+        <x:v>{"answer":-0.2748,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="J35" s="114" t="n">
+        <x:v>0.958647</x:v>
+      </x:c>
+      <x:c r="K35" s="24" t="n">
+        <x:v>0.9560000000000002</x:v>
+      </x:c>
+      <x:c r="L35" s="21" t="str">
+        <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="M35" s="118" t="n">
         <x:v>0.958365</x:v>
       </x:c>
-      <x:c r="F35" s="21" t="n">
-        <x:v>0.9557000000000001</x:v>
-      </x:c>
-      <x:c r="G35" s="111" t="str">
-        <x:v>{"answer":-0.274885,"unit":"dimensionless"}</x:v>
-      </x:c>
-      <x:c r="H35" s="21" t="n">
-        <x:v>0.958247</x:v>
-      </x:c>
-      <x:c r="I35" s="24" t="n">
-        <x:v>0.9555750000000001</x:v>
-      </x:c>
-      <x:c r="J35" s="114" t="str">
-        <x:v>{"answer":-0.2748,"unit":"dimensionless"}</x:v>
-      </x:c>
-      <x:c r="K35" s="24" t="n">
-        <x:v>0.958647</x:v>
-      </x:c>
-      <x:c r="L35" s="21" t="n">
-        <x:v>0.9560000000000002</x:v>
-      </x:c>
-      <x:c r="M35" s="118" t="str">
-        <x:v>{"answer":-0.27486,"unit":"dimensionless"}</x:v>
-      </x:c>
       <x:c r="N35" s="120" t="n">
-        <x:v>0.958365</x:v>
-      </x:c>
-      <x:c r="O35" s="122" t="n">
         <x:v>0.9557000000000001</x:v>
       </x:c>
     </x:row>
@@ -2537,42 +2438,39 @@
         <x:v>{"answer":0.301,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C36" s="99" t="str">
-        <x:v>spin_density：标准答案 0.301 dimensionless；版本 linear_goal_v2。满分：x=0.301 dimensionless。部分分：相对误差小于 80% 按距离线性递减。0分：相对误差大于等于 80%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D36" s="99" t="str">
         <x:v>{"answer":0.284262,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D36" s="99" t="n">
+        <x:v>0.93049</x:v>
+      </x:c>
       <x:c r="E36" s="24" t="n">
-        <x:v>0.93049</x:v>
-      </x:c>
-      <x:c r="F36" s="21" t="n">
         <x:v>0.9163100000000002</x:v>
       </x:c>
-      <x:c r="G36" s="111" t="str">
+      <x:c r="F36" s="21" t="str">
         <x:v>{"answer":0.284321053217,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G36" s="111" t="n">
+        <x:v>0.930735</x:v>
+      </x:c>
       <x:c r="H36" s="21" t="n">
-        <x:v>0.930735</x:v>
-      </x:c>
-      <x:c r="I36" s="24" t="n">
         <x:v>0.9166052660850001</x:v>
       </x:c>
-      <x:c r="J36" s="114" t="str">
+      <x:c r="I36" s="24" t="str">
         <x:v>{"answer":0.2244,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J36" s="114" t="n">
+        <x:v>0.681894</x:v>
+      </x:c>
       <x:c r="K36" s="24" t="n">
-        <x:v>0.681894</x:v>
-      </x:c>
-      <x:c r="L36" s="21" t="n">
         <x:v>0.617</x:v>
       </x:c>
-      <x:c r="M36" s="118" t="str">
+      <x:c r="L36" s="21" t="str">
         <x:v>{"answer":0.2842,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="M36" s="118" t="n">
+        <x:v>0.930233</x:v>
+      </x:c>
       <x:c r="N36" s="120" t="n">
-        <x:v>0.930233</x:v>
-      </x:c>
-      <x:c r="O36" s="122" t="n">
         <x:v>0.9160000000000001</x:v>
       </x:c>
     </x:row>
@@ -2584,42 +2482,39 @@
         <x:v>{"answer":0.415,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C37" s="99" t="str">
-        <x:v>spin_density：标准答案 0.415 dimensionless；版本 linear_goal_v2。满分：x=0.415 dimensionless。部分分：相对误差小于 80% 按距离线性递减。0分：相对误差大于等于 80%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D37" s="99" t="str">
         <x:v>{"answer":0.44484621905874866,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D37" s="99" t="n">
+        <x:v>0.910102</x:v>
+      </x:c>
       <x:c r="E37" s="24" t="n">
-        <x:v>0.910102</x:v>
-      </x:c>
-      <x:c r="F37" s="21" t="n">
         <x:v>0.8507689047062565</x:v>
       </x:c>
-      <x:c r="G37" s="111" t="str">
+      <x:c r="F37" s="21" t="str">
         <x:v>{"answer":0.6829546990237992,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G37" s="111" t="n">
+        <x:v>0.192908</x:v>
+      </x:c>
       <x:c r="H37" s="21" t="n">
-        <x:v>0.192908</x:v>
-      </x:c>
-      <x:c r="I37" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J37" s="114" t="str">
+      <x:c r="I37" s="24" t="str">
         <x:v>{"answer":0.445,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J37" s="114" t="n">
+        <x:v>0.909639</x:v>
+      </x:c>
       <x:c r="K37" s="24" t="n">
-        <x:v>0.909639</x:v>
-      </x:c>
-      <x:c r="L37" s="21" t="n">
         <x:v>0.8499999999999999</x:v>
       </x:c>
-      <x:c r="M37" s="118" t="str">
+      <x:c r="L37" s="21" t="str">
         <x:v>{"answer":0.4449,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="M37" s="118" t="n">
+        <x:v>0.90994</x:v>
+      </x:c>
       <x:c r="N37" s="120" t="n">
-        <x:v>0.90994</x:v>
-      </x:c>
-      <x:c r="O37" s="122" t="n">
         <x:v>0.8504999999999998</x:v>
       </x:c>
     </x:row>
@@ -2631,42 +2526,39 @@
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C38" s="99" t="str">
-        <x:v>fukui_function：标准答案 0.076 dimensionless；版本 linear_goal_v2。满分：x=0.076 dimensionless。部分分：相对误差小于 100% 按距离线性递减。0分：相对误差大于等于 100%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D38" s="99" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D38" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E38" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F38" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G38" s="111" t="str">
+      <x:c r="F38" s="21" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G38" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H38" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I38" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J38" s="114" t="str">
+      <x:c r="I38" s="24" t="str">
         <x:v>{"answer":0.076,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J38" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K38" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L38" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M38" s="118" t="str">
+      <x:c r="L38" s="21" t="str">
         <x:v>{"answer":0.0759,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="M38" s="118" t="n">
+        <x:v>0.998684</x:v>
+      </x:c>
       <x:c r="N38" s="120" t="n">
-        <x:v>0.998684</x:v>
-      </x:c>
-      <x:c r="O38" s="122" t="n">
         <x:v>0.998</x:v>
       </x:c>
     </x:row>
@@ -2678,42 +2570,39 @@
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C39" s="99" t="str">
-        <x:v>fukui_function：标准答案 0.055 dimensionless；版本 linear_goal_v2。满分：x=0.055 dimensionless。部分分：相对误差小于 100% 按距离线性递减。0分：相对误差大于等于 100%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D39" s="99" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D39" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E39" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F39" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G39" s="111" t="str">
+      <x:c r="F39" s="21" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G39" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H39" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I39" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J39" s="114" t="str">
+      <x:c r="I39" s="24" t="str">
         <x:v>{"answer":0.055,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J39" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K39" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L39" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M39" s="118" t="str">
+      <x:c r="L39" s="21" t="str">
         <x:v>{"answer":0.0539,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="M39" s="118" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
       <x:c r="N39" s="120" t="n">
-        <x:v>0.98</x:v>
-      </x:c>
-      <x:c r="O39" s="122" t="n">
         <x:v>0.9780000000000001</x:v>
       </x:c>
     </x:row>
@@ -2725,42 +2614,39 @@
         <x:v>{"answer":0.07,"unit":"dimensionless"}</x:v>
       </x:c>
       <x:c r="C40" s="99" t="str">
-        <x:v>fukui_function：标准答案 0.07 dimensionless；版本 linear_goal_v2。满分：x=0.07 dimensionless。部分分：相对误差小于 100% 按距离线性递减。0分：相对误差大于等于 100%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D40" s="99" t="str">
         <x:v>{"answer":0.070,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="D40" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E40" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F40" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G40" s="111" t="str">
+      <x:c r="F40" s="21" t="str">
         <x:v>{"answer":0.070,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="G40" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H40" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I40" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J40" s="114" t="str">
+      <x:c r="I40" s="24" t="str">
         <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
       </x:c>
+      <x:c r="J40" s="114" t="n">
+        <x:v>0.985714</x:v>
+      </x:c>
       <x:c r="K40" s="24" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="L40" s="21" t="str">
+        <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
+      </x:c>
+      <x:c r="M40" s="118" t="n">
         <x:v>0.985714</x:v>
       </x:c>
-      <x:c r="L40" s="21" t="n">
-        <x:v>0.98</x:v>
-      </x:c>
-      <x:c r="M40" s="118" t="str">
-        <x:v>{"answer":0.069,"unit":"dimensionless"}</x:v>
-      </x:c>
       <x:c r="N40" s="120" t="n">
-        <x:v>0.985714</x:v>
-      </x:c>
-      <x:c r="O40" s="122" t="n">
         <x:v>0.98</x:v>
       </x:c>
     </x:row>
@@ -2772,42 +2658,39 @@
         <x:v>{"answer":64.67,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C41" s="99" t="str">
-        <x:v>standard_entropy：标准答案 64.67 cal/(mol*K)；版本 linear_goal_v2。满分：x=64.67 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D41" s="99" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D41" s="99" t="n">
+        <x:v>0.957476</x:v>
+      </x:c>
       <x:c r="E41" s="24" t="n">
+        <x:v>0.9489717024895626</x:v>
+      </x:c>
+      <x:c r="F41" s="21" t="str">
+        <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="G41" s="111" t="n">
         <x:v>0.957476</x:v>
       </x:c>
-      <x:c r="F41" s="21" t="n">
+      <x:c r="H41" s="21" t="n">
         <x:v>0.9489717024895626</x:v>
       </x:c>
-      <x:c r="G41" s="111" t="str">
+      <x:c r="I41" s="24" t="str">
         <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="H41" s="21" t="n">
+      <x:c r="J41" s="114" t="n">
         <x:v>0.957476</x:v>
       </x:c>
-      <x:c r="I41" s="24" t="n">
+      <x:c r="K41" s="24" t="n">
         <x:v>0.9489717024895626</x:v>
       </x:c>
-      <x:c r="J41" s="114" t="str">
-        <x:v>{"answer":64.34,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
-      <x:c r="K41" s="24" t="n">
-        <x:v>0.957476</x:v>
-      </x:c>
-      <x:c r="L41" s="21" t="n">
-        <x:v>0.9489717024895626</x:v>
-      </x:c>
-      <x:c r="M41" s="118" t="str">
+      <x:c r="L41" s="21" t="str">
         <x:v>{"answer":64.37,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="M41" s="118" t="n">
+        <x:v>0.961342</x:v>
+      </x:c>
       <x:c r="N41" s="120" t="n">
-        <x:v>0.961342</x:v>
-      </x:c>
-      <x:c r="O41" s="122" t="n">
         <x:v>0.9536106386268753</x:v>
       </x:c>
     </x:row>
@@ -2819,42 +2702,39 @@
         <x:v>{"answer":57.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C42" s="99" t="str">
-        <x:v>standard_entropy：标准答案 57.88 cal/(mol*K)；版本 linear_goal_v2。满分：x=57.88 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D42" s="99" t="str">
         <x:v>{"answer":58.04,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D42" s="99" t="n">
+        <x:v>0.976964</x:v>
+      </x:c>
       <x:c r="E42" s="24" t="n">
-        <x:v>0.976964</x:v>
-      </x:c>
-      <x:c r="F42" s="21" t="n">
         <x:v>0.9723565998617836</x:v>
       </x:c>
-      <x:c r="G42" s="111" t="str">
+      <x:c r="F42" s="21" t="str">
         <x:v>{"answer":58.01,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="G42" s="111" t="n">
+        <x:v>0.981283</x:v>
+      </x:c>
       <x:c r="H42" s="21" t="n">
-        <x:v>0.981283</x:v>
-      </x:c>
-      <x:c r="I42" s="24" t="n">
         <x:v>0.9775397373876995</x:v>
       </x:c>
-      <x:c r="J42" s="114" t="str">
+      <x:c r="I42" s="24" t="str">
         <x:v>{"answer":57.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="J42" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K42" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L42" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M42" s="118" t="str">
+      <x:c r="L42" s="21" t="str">
         <x:v>{"answer":58.17,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="M42" s="118" t="n">
+        <x:v>0.958247</x:v>
+      </x:c>
       <x:c r="N42" s="120" t="n">
-        <x:v>0.958247</x:v>
-      </x:c>
-      <x:c r="O42" s="122" t="n">
         <x:v>0.9498963372494819</x:v>
       </x:c>
     </x:row>
@@ -2866,42 +2746,39 @@
         <x:v>{"answer":73.88,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C43" s="99" t="str">
-        <x:v>standard_entropy：标准答案 73.88 cal/(mol*K)；版本 linear_goal_v2。满分：x=73.88 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D43" s="99" t="str">
         <x:v>{"answer":73.14,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D43" s="99" t="n">
+        <x:v>0.916531</x:v>
+      </x:c>
       <x:c r="E43" s="24" t="n">
-        <x:v>0.916531</x:v>
-      </x:c>
-      <x:c r="F43" s="21" t="n">
         <x:v>0.8998375744450468</x:v>
       </x:c>
-      <x:c r="G43" s="111" t="str">
+      <x:c r="F43" s="21" t="str">
         <x:v>{"answer":75.22,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="G43" s="111" t="n">
+        <x:v>0.848854</x:v>
+      </x:c>
       <x:c r="H43" s="21" t="n">
-        <x:v>0.848854</x:v>
-      </x:c>
-      <x:c r="I43" s="24" t="n">
         <x:v>0.8186247969680558</x:v>
       </x:c>
-      <x:c r="J43" s="114" t="str">
+      <x:c r="I43" s="24" t="str">
         <x:v>{"answer":73.85,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="J43" s="114" t="n">
+        <x:v>0.996616</x:v>
+      </x:c>
       <x:c r="K43" s="24" t="n">
-        <x:v>0.996616</x:v>
-      </x:c>
-      <x:c r="L43" s="21" t="n">
         <x:v>0.9959393611261503</x:v>
       </x:c>
-      <x:c r="M43" s="118" t="str">
+      <x:c r="L43" s="21" t="str">
         <x:v>{"answer":73.5,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="M43" s="118" t="n">
+        <x:v>0.957138</x:v>
+      </x:c>
       <x:c r="N43" s="120" t="n">
-        <x:v>0.957138</x:v>
-      </x:c>
-      <x:c r="O43" s="122" t="n">
         <x:v>0.9485652409312405</x:v>
       </x:c>
     </x:row>
@@ -2913,42 +2790,39 @@
         <x:v>{"answer":44.4,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C44" s="99" t="str">
-        <x:v>standard_entropy：标准答案 44.4 cal/(mol*K)；版本 linear_goal_v2。满分：x=44.4 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D44" s="99" t="str">
         <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D44" s="99" t="n">
+        <x:v>0.977477</x:v>
+      </x:c>
       <x:c r="E44" s="24" t="n">
+        <x:v>0.9729729729729719</x:v>
+      </x:c>
+      <x:c r="F44" s="21" t="str">
+        <x:v>{"answer":44.516,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="G44" s="111" t="n">
+        <x:v>0.978228</x:v>
+      </x:c>
+      <x:c r="H44" s="21" t="n">
+        <x:v>0.9738738738738739</x:v>
+      </x:c>
+      <x:c r="I44" s="24" t="str">
+        <x:v>{"answer":44.5,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="J44" s="114" t="n">
+        <x:v>0.981231</x:v>
+      </x:c>
+      <x:c r="K44" s="24" t="n">
+        <x:v>0.9774774774774772</x:v>
+      </x:c>
+      <x:c r="L44" s="21" t="str">
+        <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="M44" s="118" t="n">
         <x:v>0.977477</x:v>
       </x:c>
-      <x:c r="F44" s="21" t="n">
-        <x:v>0.9729729729729719</x:v>
-      </x:c>
-      <x:c r="G44" s="111" t="str">
-        <x:v>{"answer":44.516,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
-      <x:c r="H44" s="21" t="n">
-        <x:v>0.978228</x:v>
-      </x:c>
-      <x:c r="I44" s="24" t="n">
-        <x:v>0.9738738738738739</x:v>
-      </x:c>
-      <x:c r="J44" s="114" t="str">
-        <x:v>{"answer":44.5,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
-      <x:c r="K44" s="24" t="n">
-        <x:v>0.981231</x:v>
-      </x:c>
-      <x:c r="L44" s="21" t="n">
-        <x:v>0.9774774774774772</x:v>
-      </x:c>
-      <x:c r="M44" s="118" t="str">
-        <x:v>{"answer":44.52,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
       <x:c r="N44" s="120" t="n">
-        <x:v>0.977477</x:v>
-      </x:c>
-      <x:c r="O44" s="122" t="n">
         <x:v>0.9729729729729719</x:v>
       </x:c>
     </x:row>
@@ -2960,42 +2834,39 @@
         <x:v>{"answer":45.92,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C45" s="99" t="str">
-        <x:v>standard_entropy：标准答案 45.92 cal/(mol*K)；版本 linear_goal_v2。满分：x=45.92 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D45" s="99" t="str">
         <x:v>{"answer":46.073136,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D45" s="99" t="n">
+        <x:v>0.97221</x:v>
+      </x:c>
       <x:c r="E45" s="24" t="n">
-        <x:v>0.97221</x:v>
-      </x:c>
-      <x:c r="F45" s="21" t="n">
         <x:v>0.9666515679442517</x:v>
       </x:c>
-      <x:c r="G45" s="111" t="str">
+      <x:c r="F45" s="21" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="G45" s="111" t="n">
+        <x:v>0.972779</x:v>
+      </x:c>
       <x:c r="H45" s="21" t="n">
+        <x:v>0.9673344947735195</x:v>
+      </x:c>
+      <x:c r="I45" s="24" t="str">
+        <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="J45" s="114" t="n">
         <x:v>0.972779</x:v>
       </x:c>
-      <x:c r="I45" s="24" t="n">
+      <x:c r="K45" s="24" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
-      <x:c r="J45" s="114" t="str">
+      <x:c r="L45" s="21" t="str">
         <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K45" s="24" t="n">
+      <x:c r="M45" s="118" t="n">
         <x:v>0.972779</x:v>
       </x:c>
-      <x:c r="L45" s="21" t="n">
-        <x:v>0.9673344947735195</x:v>
-      </x:c>
-      <x:c r="M45" s="118" t="str">
-        <x:v>{"answer":46.07,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
       <x:c r="N45" s="120" t="n">
-        <x:v>0.972779</x:v>
-      </x:c>
-      <x:c r="O45" s="122" t="n">
         <x:v>0.9673344947735195</x:v>
       </x:c>
     </x:row>
@@ -3007,42 +2878,39 @@
         <x:v>{"answer":51.18,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
       <x:c r="C46" s="99" t="str">
-        <x:v>standard_entropy：标准答案 51.18 cal/(mol*K)；版本 linear_goal_v2。满分：x=51.18 cal/(mol*K)。部分分：相对误差小于 12% 按距离线性递减。0分：相对误差大于等于 12%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D46" s="99" t="str">
         <x:v>{"answer":51.095841,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="D46" s="99" t="n">
+        <x:v>0.986297</x:v>
+      </x:c>
       <x:c r="E46" s="24" t="n">
-        <x:v>0.986297</x:v>
-      </x:c>
-      <x:c r="F46" s="21" t="n">
         <x:v>0.9835562719812427</x:v>
       </x:c>
-      <x:c r="G46" s="111" t="str">
+      <x:c r="F46" s="21" t="str">
         <x:v>{"answer":51.10,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
+      <x:c r="G46" s="111" t="n">
+        <x:v>0.986974</x:v>
+      </x:c>
       <x:c r="H46" s="21" t="n">
+        <x:v>0.9843688940992579</x:v>
+      </x:c>
+      <x:c r="I46" s="24" t="str">
+        <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
+      </x:c>
+      <x:c r="J46" s="114" t="n">
         <x:v>0.986974</x:v>
       </x:c>
-      <x:c r="I46" s="24" t="n">
+      <x:c r="K46" s="24" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
-      <x:c r="J46" s="114" t="str">
+      <x:c r="L46" s="21" t="str">
         <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
       </x:c>
-      <x:c r="K46" s="24" t="n">
+      <x:c r="M46" s="118" t="n">
         <x:v>0.986974</x:v>
       </x:c>
-      <x:c r="L46" s="21" t="n">
-        <x:v>0.9843688940992579</x:v>
-      </x:c>
-      <x:c r="M46" s="118" t="str">
-        <x:v>{"answer":51.1,"unit":"cal/(mol*K)"}</x:v>
-      </x:c>
       <x:c r="N46" s="120" t="n">
-        <x:v>0.986974</x:v>
-      </x:c>
-      <x:c r="O46" s="122" t="n">
         <x:v>0.9843688940992579</x:v>
       </x:c>
     </x:row>
@@ -3054,42 +2922,39 @@
         <x:v>{"answer":-16.04,"unit":"kcal/mol"}</x:v>
       </x:c>
       <x:c r="C47" s="99" t="str">
-        <x:v>dimerization_enthalpy：标准答案 -16.04 kcal/mol；版本 linear_goal_v2。满分：x=-16.04 kcal/mol。部分分：-19.04 &lt; x &lt; -16.04 或 -16.04 &lt; x &lt; -13.04（按绝对误差线性递减）。0分：x &lt;= -19.04 或 x &gt;= -13.04；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D47" s="99" t="str">
         <x:v>{"answer":-16.0426,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="D47" s="99" t="n">
+        <x:v>0.999133</x:v>
+      </x:c>
       <x:c r="E47" s="24" t="n">
-        <x:v>0.999133</x:v>
-      </x:c>
-      <x:c r="F47" s="21" t="n">
         <x:v>0.999133333333333</x:v>
       </x:c>
-      <x:c r="G47" s="111" t="str">
+      <x:c r="F47" s="21" t="str">
         <x:v>{"answer":-16.04,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="G47" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H47" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I47" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J47" s="114" t="str">
+      <x:c r="I47" s="24" t="str">
         <x:v>{"answer":-16.13,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="J47" s="114" t="n">
+        <x:v>0.97</x:v>
+      </x:c>
       <x:c r="K47" s="24" t="n">
-        <x:v>0.97</x:v>
-      </x:c>
-      <x:c r="L47" s="21" t="n">
         <x:v>0.9700000000000001</x:v>
       </x:c>
-      <x:c r="M47" s="118" t="str">
+      <x:c r="L47" s="21" t="str">
         <x:v>{"answer":-17.2,"unit":"kcal/mol"}</x:v>
       </x:c>
+      <x:c r="M47" s="118" t="n">
+        <x:v>0.613333</x:v>
+      </x:c>
       <x:c r="N47" s="120" t="n">
-        <x:v>0.613333</x:v>
-      </x:c>
-      <x:c r="O47" s="122" t="n">
         <x:v>0.6133333333333333</x:v>
       </x:c>
     </x:row>
@@ -3101,42 +2966,39 @@
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
       <x:c r="C48" s="99" t="str">
-        <x:v>most_negative_mulliken_atom：标准答案 "11 O"；版本 linear_goal_v2。与标准字符串完全一致得 1 分；其他结果得 0 分。</x:v>
-      </x:c>
-      <x:c r="D48" s="99" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
+      <x:c r="D48" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E48" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F48" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G48" s="111" t="str">
+      <x:c r="F48" s="21" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
+      <x:c r="G48" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H48" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I48" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J48" s="114" t="str">
+      <x:c r="I48" s="24" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
+      <x:c r="J48" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K48" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L48" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M48" s="118" t="str">
+      <x:c r="L48" s="21" t="str">
         <x:v>{"answer":"11 O"}</x:v>
       </x:c>
+      <x:c r="M48" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N48" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O48" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3148,42 +3010,39 @@
         <x:v>{"answer":0.364,"unit":"e"}</x:v>
       </x:c>
       <x:c r="C49" s="99" t="str">
-        <x:v>mulliken_charge：标准答案 0.364 e；版本 linear_goal_v2。满分：x=0.364 e。部分分：相对误差小于 75% 按距离线性递减。0分：相对误差大于等于 75%、单位不匹配或值无效。</x:v>
-      </x:c>
-      <x:c r="D49" s="99" t="str">
         <x:v>{"answer":0.36363323,"unit":"e"}</x:v>
       </x:c>
+      <x:c r="D49" s="99" t="n">
+        <x:v>0.998657</x:v>
+      </x:c>
       <x:c r="E49" s="24" t="n">
-        <x:v>0.998657</x:v>
-      </x:c>
-      <x:c r="F49" s="21" t="n">
         <x:v>0.9975548666666666</x:v>
       </x:c>
-      <x:c r="G49" s="111" t="str">
+      <x:c r="F49" s="21" t="str">
         <x:v>{"answer":0.3636,"unit":"e"}</x:v>
       </x:c>
+      <x:c r="G49" s="111" t="n">
+        <x:v>0.998535</x:v>
+      </x:c>
       <x:c r="H49" s="21" t="n">
-        <x:v>0.998535</x:v>
-      </x:c>
-      <x:c r="I49" s="24" t="n">
         <x:v>0.9973333333333333</x:v>
       </x:c>
-      <x:c r="J49" s="114" t="str">
+      <x:c r="I49" s="24" t="str">
         <x:v>{"answer":0.3637,"unit":"e"}</x:v>
       </x:c>
+      <x:c r="J49" s="114" t="n">
+        <x:v>0.998901</x:v>
+      </x:c>
       <x:c r="K49" s="24" t="n">
-        <x:v>0.998901</x:v>
-      </x:c>
-      <x:c r="L49" s="21" t="n">
         <x:v>0.9980000000000002</x:v>
       </x:c>
-      <x:c r="M49" s="118" t="str">
+      <x:c r="L49" s="21" t="str">
         <x:v>{"answer":0.364,"unit":"e"}</x:v>
       </x:c>
+      <x:c r="M49" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N49" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O49" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3195,42 +3054,39 @@
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
       <x:c r="C50" s="99" t="str">
-        <x:v>most_negative_mulliken_atom：标准答案 "3 N"；版本 linear_goal_v2。与标准字符串完全一致得 1 分；其他结果得 0 分。</x:v>
-      </x:c>
-      <x:c r="D50" s="99" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
+      <x:c r="D50" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E50" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F50" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G50" s="111" t="str">
+      <x:c r="F50" s="21" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
+      <x:c r="G50" s="111" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H50" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I50" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J50" s="114" t="str">
+      <x:c r="I50" s="24" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
+      <x:c r="J50" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K50" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L50" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M50" s="118" t="str">
+      <x:c r="L50" s="21" t="str">
         <x:v>{"answer":"3 N"}</x:v>
       </x:c>
+      <x:c r="M50" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N50" s="120" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O50" s="122" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3242,42 +3098,39 @@
         <x:v>{"answer":4.12,"unit":"eV"}</x:v>
       </x:c>
       <x:c r="C51" s="99" t="str">
-        <x:v>vertical_excitation_energy：标准答案 4.12 eV；版本 linear_goal_v2。满分：x=4.12 eV。部分分：3.12 &lt; x &lt; 4.12 或 4.12 &lt; x &lt; 5.12（按绝对误差线性递减）。0分：x &lt;= 3.12 或 x &gt;= 5.12；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D51" s="99" t="str">
         <x:v>{"answer":4.078,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="D51" s="99" t="n">
+        <x:v>0.958</x:v>
+      </x:c>
       <x:c r="E51" s="24" t="n">
+        <x:v>0.9160000000000004</x:v>
+      </x:c>
+      <x:c r="F51" s="21" t="str">
+        <x:v>{"answer":4.08,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="G51" s="111" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="H51" s="21" t="n">
+        <x:v>0.9199999999999999</x:v>
+      </x:c>
+      <x:c r="I51" s="24" t="str">
+        <x:v>{"answer":4.078,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="J51" s="114" t="n">
         <x:v>0.958</x:v>
       </x:c>
-      <x:c r="F51" s="21" t="n">
+      <x:c r="K51" s="24" t="n">
         <x:v>0.9160000000000004</x:v>
       </x:c>
-      <x:c r="G51" s="111" t="str">
+      <x:c r="L51" s="21" t="str">
         <x:v>{"answer":4.08,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="H51" s="21" t="n">
+      <x:c r="M51" s="118" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="I51" s="24" t="n">
-        <x:v>0.9199999999999999</x:v>
-      </x:c>
-      <x:c r="J51" s="114" t="str">
-        <x:v>{"answer":4.078,"unit":"eV"}</x:v>
-      </x:c>
-      <x:c r="K51" s="24" t="n">
-        <x:v>0.958</x:v>
-      </x:c>
-      <x:c r="L51" s="21" t="n">
-        <x:v>0.9160000000000004</x:v>
-      </x:c>
-      <x:c r="M51" s="118" t="str">
-        <x:v>{"answer":4.08,"unit":"eV"}</x:v>
-      </x:c>
       <x:c r="N51" s="120" t="n">
-        <x:v>0.96</x:v>
-      </x:c>
-      <x:c r="O51" s="122" t="n">
         <x:v>0.9199999999999999</x:v>
       </x:c>
     </x:row>
@@ -3289,42 +3142,39 @@
         <x:v>{"answer":4.42,"unit":"eV"}</x:v>
       </x:c>
       <x:c r="C52" s="99" t="str">
-        <x:v>vertical_excitation_energy：标准答案 4.42 eV；版本 linear_goal_v2。满分：x=4.42 eV。部分分：3.42 &lt; x &lt; 4.42 或 4.42 &lt; x &lt; 5.42（按绝对误差线性递减）。0分：x &lt;= 3.42 或 x &gt;= 5.42；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D52" s="99" t="str">
         <x:v>{"answer":4.3656,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="D52" s="99" t="n">
+        <x:v>0.9456</x:v>
+      </x:c>
       <x:c r="E52" s="24" t="n">
-        <x:v>0.9456</x:v>
-      </x:c>
-      <x:c r="F52" s="21" t="n">
         <x:v>0.8911999999999995</x:v>
       </x:c>
-      <x:c r="G52" s="111" t="str">
+      <x:c r="F52" s="21" t="str">
         <x:v>{"answer":4.3655,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="G52" s="111" t="n">
+        <x:v>0.9455</x:v>
+      </x:c>
       <x:c r="H52" s="21" t="n">
-        <x:v>0.9455</x:v>
-      </x:c>
-      <x:c r="I52" s="24" t="n">
         <x:v>0.891</x:v>
       </x:c>
-      <x:c r="J52" s="114" t="str">
+      <x:c r="I52" s="24" t="str">
         <x:v>{"answer":4.37,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="J52" s="114" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
       <x:c r="K52" s="24" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="L52" s="21" t="n">
         <x:v>0.9000000000000004</x:v>
       </x:c>
-      <x:c r="M52" s="118" t="str">
+      <x:c r="L52" s="21" t="str">
         <x:v>{"answer":4.3657,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="M52" s="118" t="n">
+        <x:v>0.9457</x:v>
+      </x:c>
       <x:c r="N52" s="120" t="n">
-        <x:v>0.9457</x:v>
-      </x:c>
-      <x:c r="O52" s="122" t="n">
         <x:v>0.8914000000000009</x:v>
       </x:c>
     </x:row>
@@ -3336,42 +3186,39 @@
         <x:v>{"answer":4.51,"unit":"eV"}</x:v>
       </x:c>
       <x:c r="C53" s="99" t="str">
-        <x:v>vertical_excitation_energy：标准答案 4.51 eV；版本 linear_goal_v2。满分：x=4.51 eV。部分分：3.51 &lt; x &lt; 4.51 或 4.51 &lt; x &lt; 5.51（按绝对误差线性递减）。0分：x &lt;= 3.51 或 x &gt;= 5.51；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D53" s="99" t="str">
         <x:v>{"answer":4.4488,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="D53" s="99" t="n">
+        <x:v>0.9388</x:v>
+      </x:c>
       <x:c r="E53" s="24" t="n">
-        <x:v>0.9388</x:v>
-      </x:c>
-      <x:c r="F53" s="21" t="n">
         <x:v>0.877600000000001</x:v>
       </x:c>
-      <x:c r="G53" s="111" t="str">
+      <x:c r="F53" s="21" t="str">
         <x:v>{"answer":4.44869,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="G53" s="111" t="n">
+        <x:v>0.93869</x:v>
+      </x:c>
       <x:c r="H53" s="21" t="n">
-        <x:v>0.93869</x:v>
-      </x:c>
-      <x:c r="I53" s="24" t="n">
         <x:v>0.8773800000000005</x:v>
       </x:c>
-      <x:c r="J53" s="114" t="str">
+      <x:c r="I53" s="24" t="str">
         <x:v>{"answer":4.449,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="J53" s="114" t="n">
+        <x:v>0.939</x:v>
+      </x:c>
       <x:c r="K53" s="24" t="n">
+        <x:v>0.8780000000000001</x:v>
+      </x:c>
+      <x:c r="L53" s="21" t="str">
+        <x:v>{"answer":4.449,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="M53" s="118" t="n">
         <x:v>0.939</x:v>
       </x:c>
-      <x:c r="L53" s="21" t="n">
-        <x:v>0.8780000000000001</x:v>
-      </x:c>
-      <x:c r="M53" s="118" t="str">
-        <x:v>{"answer":4.449,"unit":"eV"}</x:v>
-      </x:c>
       <x:c r="N53" s="120" t="n">
-        <x:v>0.939</x:v>
-      </x:c>
-      <x:c r="O53" s="122" t="n">
         <x:v>0.8780000000000001</x:v>
       </x:c>
     </x:row>
@@ -3383,42 +3230,39 @@
         <x:v>{"answer":4.04,"unit":"eV"}</x:v>
       </x:c>
       <x:c r="C54" s="99" t="str">
-        <x:v>vertical_excitation_energy：标准答案 4.04 eV；版本 linear_goal_v2。满分：x=4.04 eV。部分分：3.04 &lt; x &lt; 4.04 或 4.04 &lt; x &lt; 5.04（按绝对误差线性递减）。0分：x &lt;= 3.04 或 x &gt;= 5.04；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D54" s="99" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="D54" s="99" t="n">
+        <x:v>0.961</x:v>
+      </x:c>
       <x:c r="E54" s="24" t="n">
+        <x:v>0.9220000000000006</x:v>
+      </x:c>
+      <x:c r="F54" s="21" t="str">
+        <x:v>{"answer":4.001,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="G54" s="111" t="n">
         <x:v>0.961</x:v>
       </x:c>
-      <x:c r="F54" s="21" t="n">
+      <x:c r="H54" s="21" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
-      <x:c r="G54" s="111" t="str">
+      <x:c r="I54" s="24" t="str">
+        <x:v>{"answer":3.86,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="J54" s="114" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="K54" s="24" t="n">
+        <x:v>0.6399999999999997</x:v>
+      </x:c>
+      <x:c r="L54" s="21" t="str">
         <x:v>{"answer":4.001,"unit":"eV"}</x:v>
       </x:c>
-      <x:c r="H54" s="21" t="n">
+      <x:c r="M54" s="118" t="n">
         <x:v>0.961</x:v>
       </x:c>
-      <x:c r="I54" s="24" t="n">
-        <x:v>0.9220000000000006</x:v>
-      </x:c>
-      <x:c r="J54" s="114" t="str">
-        <x:v>{"answer":3.86,"unit":"eV"}</x:v>
-      </x:c>
-      <x:c r="K54" s="24" t="n">
-        <x:v>0.82</x:v>
-      </x:c>
-      <x:c r="L54" s="21" t="n">
-        <x:v>0.6399999999999997</x:v>
-      </x:c>
-      <x:c r="M54" s="118" t="str">
-        <x:v>{"answer":4.001,"unit":"eV"}</x:v>
-      </x:c>
       <x:c r="N54" s="120" t="n">
-        <x:v>0.961</x:v>
-      </x:c>
-      <x:c r="O54" s="122" t="n">
         <x:v>0.9220000000000006</x:v>
       </x:c>
     </x:row>
@@ -3430,42 +3274,39 @@
         <x:v>{"answer":3.39,"unit":"eV"}</x:v>
       </x:c>
       <x:c r="C55" s="100" t="str">
-        <x:v>vertical_excitation_energy：标准答案 3.39 eV；版本 linear_goal_v2。满分：x=3.39 eV。部分分：2.39 &lt; x &lt; 3.39 或 3.39 &lt; x &lt; 4.39（按绝对误差线性递减）。0分：x &lt;= 2.39 或 x &gt;= 4.39；单位不匹配或值无效也为0分。</x:v>
-      </x:c>
-      <x:c r="D55" s="100" t="str">
         <x:v>{"answer":3.36,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="D55" s="100" t="n">
+        <x:v>0.97</x:v>
+      </x:c>
       <x:c r="E55" s="25" t="n">
+        <x:v>0.9399999999999995</x:v>
+      </x:c>
+      <x:c r="F55" s="22" t="str">
+        <x:v>{"answer":3.36,"unit":"eV"}</x:v>
+      </x:c>
+      <x:c r="G55" s="112" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="F55" s="22" t="n">
+      <x:c r="H55" s="22" t="n">
         <x:v>0.9399999999999995</x:v>
       </x:c>
-      <x:c r="G55" s="112" t="str">
-        <x:v>{"answer":3.36,"unit":"eV"}</x:v>
-      </x:c>
-      <x:c r="H55" s="22" t="n">
-        <x:v>0.97</x:v>
-      </x:c>
-      <x:c r="I55" s="25" t="n">
-        <x:v>0.9399999999999995</x:v>
-      </x:c>
-      <x:c r="J55" s="115" t="str">
+      <x:c r="I55" s="25" t="str">
         <x:v>{"answer":3.358,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="J55" s="115" t="n">
+        <x:v>0.968</x:v>
+      </x:c>
       <x:c r="K55" s="25" t="n">
-        <x:v>0.968</x:v>
-      </x:c>
-      <x:c r="L55" s="22" t="n">
         <x:v>0.9359999999999999</x:v>
       </x:c>
-      <x:c r="M55" s="119" t="str">
+      <x:c r="L55" s="22" t="str">
         <x:v>{"answer":3.357,"unit":"eV"}</x:v>
       </x:c>
+      <x:c r="M55" s="119" t="n">
+        <x:v>0.967</x:v>
+      </x:c>
       <x:c r="N55" s="121" t="n">
-        <x:v>0.967</x:v>
-      </x:c>
-      <x:c r="O55" s="55" t="n">
         <x:v>0.9340000000000002</x:v>
       </x:c>
     </x:row>
@@ -3474,46 +3315,45 @@
         <x:v>各实验组平均分（忽略未评分项）</x:v>
       </x:c>
       <x:c r="B56" s="104"/>
-      <x:c r="C56" s="104"/>
-      <x:c r="D56" s="106" t="str">
+      <x:c r="C56" s="104" t="str">
         <x:v>平均分</x:v>
       </x:c>
+      <x:c r="D56" s="106" t="n">
+        <x:v>0.912676</x:v>
+      </x:c>
       <x:c r="E56" s="23" t="n">
-        <x:v>0.912676</x:v>
-      </x:c>
-      <x:c r="F56" s="23" t="n">
         <x:v>0.8606945680337507</x:v>
       </x:c>
-      <x:c r="G56" s="113" t="str">
+      <x:c r="F56" s="23" t="str">
         <x:v>平均分</x:v>
       </x:c>
+      <x:c r="G56" s="113" t="n">
+        <x:v>0.915456</x:v>
+      </x:c>
       <x:c r="H56" s="23" t="n">
-        <x:v>0.915456</x:v>
-      </x:c>
-      <x:c r="I56" s="23" t="n">
         <x:v>0.8825376152069491</x:v>
       </x:c>
-      <x:c r="J56" s="106" t="str">
+      <x:c r="I56" s="23" t="str">
         <x:v>平均分</x:v>
       </x:c>
+      <x:c r="J56" s="106" t="n">
+        <x:v>0.906391</x:v>
+      </x:c>
       <x:c r="K56" s="23" t="n">
-        <x:v>0.906391</x:v>
-      </x:c>
-      <x:c r="L56" s="23" t="n">
         <x:v>0.8647874743370195</x:v>
       </x:c>
-      <x:c r="M56" s="79" t="str">
+      <x:c r="L56" s="23" t="str">
         <x:v>平均分</x:v>
       </x:c>
+      <x:c r="M56" s="79" t="n">
+        <x:v>0.898382</x:v>
+      </x:c>
       <x:c r="N56" s="60" t="n">
-        <x:v>0.898382</x:v>
-      </x:c>
-      <x:c r="O56" s="60" t="n">
         <x:v>0.8619780245298304</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ea6b9c913f748b8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48c08110d0854031"/>
 </x:worksheet>
 </file>